--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -564,7 +564,7 @@
         <v>44354</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45114</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>43423</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43402</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>44210</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>43472</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>43664</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>44125</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44026</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>44498</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45177</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>44470</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44854</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44861</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44960</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>43738</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>43738</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>44418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44960</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>45182</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44015</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44139</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44860</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44986</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44987</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>45016</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45191</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45201</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>43427</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>43439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43636</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>43803</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>43888</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>43936</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44082</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44082</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44393</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44393</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44501</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44764</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44817</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44823</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44925</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44985</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45112</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45113</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45113</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45208</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>43339</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>43374</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>43440</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>43445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>43473</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>43493</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>43500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>43500</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>43501</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>43504</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>43504</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>43504</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>43504</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>43507</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>43510</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>43516</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>43517</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>43517</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>43523</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>43531</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>43536</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>43539</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43544</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>43559</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>43585</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>43585</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43585</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>43585</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>43587</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43591</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43601</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>43614</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>43636</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43664</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>43664</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>43664</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43686</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43697</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43700</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43705</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>43707</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>43709</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43738</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43738</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43738</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43739</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>43740</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43748</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>43752</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>43753</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43754</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>43755</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>43760</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>43761</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>43768</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>43768</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>43769</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>43769</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43787</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43787</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43794</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43794</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43795</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43803</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43803</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43803</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>43805</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>43810</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43818</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43833</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43841</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>43843</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>43843</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>43845</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>43852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>43859</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>43888</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>43924</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>43936</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>43936</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>43961</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>43976</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>43980</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43980</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43983</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43987</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43993</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43993</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43993</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44004</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44007</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44014</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44026</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44028</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44029</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44029</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44029</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>44029</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44029</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44050</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>44054</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>44060</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44071</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44078</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44082</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44082</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>44089</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44089</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44089</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44089</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44090</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44090</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44090</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44090</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44096</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44106</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44106</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44106</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44115</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44116</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44117</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44125</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44132</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44132</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44132</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44133</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44134</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44141</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44147</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44147</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44148</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44151</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44151</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44151</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>44152</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>44161</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44163</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44166</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44168</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44170</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44170</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44175</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44186</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44193</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44207</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44210</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44211</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44218</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44218</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44230</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44231</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44231</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44231</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44323</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44328</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44341</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44344</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44344</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44344</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44350</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44350</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>44351</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44356</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44357</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44357</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>44368</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44371</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>44377</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44377</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44377</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>44377</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44377</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44377</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44377</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>44378</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44379</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44379</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44381</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>44382</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44386</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44386</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44386</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>44386</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44391</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44390</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>44391</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44390</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44392</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44393</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44393</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>44399</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>44404</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44407</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44417</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>44418</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44420</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44420</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>44420</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44424</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44426</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44426</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44426</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44428</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44433</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44433</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44438</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44438</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44449</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44449</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44453</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>44455</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44459</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44470</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44470</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>44472</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44473</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44473</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44474</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44476</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44476</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44477</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44477</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44483</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44489</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>44490</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44490</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44496</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44496</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>44496</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44496</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44496</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44497</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44497</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44498</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44498</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44498</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44498</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44498</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>44501</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>44503</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>44503</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>44503</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44505</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44505</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44505</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>44510</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44512</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44516</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44516</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44518</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44519</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44519</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>44519</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44523</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44524</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44525</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44526</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44526</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44526</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44530</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>44531</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44533</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44533</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44551</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>44551</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44585</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44585</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44585</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44586</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44592</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44592</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44594</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44595</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44607</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44615</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44632</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44637</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44642</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44652</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44652</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44662</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44662</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44672</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44674</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44674</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44678</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44681</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44687</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44687</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>44687</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44687</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44687</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44694</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44694</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44694</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44697</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>44698</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44698</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44701</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44708</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44708</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44708</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>44708</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44708</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44708</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>44709</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44711</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44711</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44713</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>44719</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>44722</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>44726</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44726</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44727</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44728</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44728</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>44729</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44740</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>44739</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44741</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44742</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44742</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44744</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44747</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>44747</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>44749</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>44751</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44750</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44750</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44754</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44755</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44755</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44755</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>44755</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44756</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44756</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44757</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44762</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>44761</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>44761</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>44768</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>44770</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44770</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>44774</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>44775</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>44779</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44778</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44779</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44781</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44781</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44783</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44796</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44795</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>44795</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44798</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44799</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44799</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44803</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44803</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44803</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44803</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44803</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44803</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>44806</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44807</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44809</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44809</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44813</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44813</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44813</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44813</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44814</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44816</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44816</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44816</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44816</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44818</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>44818</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44818</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>44818</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44818</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44819</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44820</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44826</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>44826</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44830</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44832</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44834</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44839</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44839</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44846</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44846</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44846</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44847</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44848</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>44847</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>44852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44855</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44858</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44858</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44859</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>44859</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>44860</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44860</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44862</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>44862</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44866</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>44868</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44872</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44872</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44876</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>44879</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>44886</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>44886</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44886</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>44887</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44888</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44888</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44894</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44908</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44908</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>44908</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44908</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>44908</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44908</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>44911</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44911</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>44915</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44917</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44917</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44922</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44925</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>44925</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>44928</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>44929</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44936</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44936</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44936</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44936</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>44936</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>44936</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44936</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44937</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44938</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44938</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>44943</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>44943</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>44943</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44943</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>44950</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44950</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44951</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44952</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>44952</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44952</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44952</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44952</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44952</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44954</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44953</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44958</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44959</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44960</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44960</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44960</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44964</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44966</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44966</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44967</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44967</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44970</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44970</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44970</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44971</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44973</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44973</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44977</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44978</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>44978</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>44977</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>44980</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44984</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44984</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44984</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44985</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44985</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44986</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44986</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44986</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44987</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44988</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>44988</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>44988</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44988</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44988</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44992</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>44993</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>44993</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>44994</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45000</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45005</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45005</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45005</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45009</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45010</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45010</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45010</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45010</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45010</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45010</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45009</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45014</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45014</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>45016</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45030</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>45035</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45036</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45037</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45038</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45040</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45041</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45042</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45042</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45044</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45044</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45048</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45051</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45061</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45068</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45068</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45068</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45068</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45068</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45068</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45072</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45072</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45072</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45077</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45077</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45077</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45077</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>45078</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45078</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45078</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45078</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45078</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45078</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>45078</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45078</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45079</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45078</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45078</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45078</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45079</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45079</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45079</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45084</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45091</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45092</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45092</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45092</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>45092</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45092</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45092</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>45092</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45092</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45093</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45093</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>45093</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45096</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45098</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45098</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45099</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45099</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45099</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45099</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45099</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45099</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45103</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45103</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45103</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45103</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45103</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45103</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45103</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45103</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45103</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45103</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45105</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45107</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45107</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45112</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>45112</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45113</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45114</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45114</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>45114</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45114</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45114</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45113</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45114</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45114</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45114</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45113</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45113</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45113</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45113</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45113</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45114</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45114</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45114</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45114</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45117</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45119</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>45119</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45119</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45119</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45120</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45120</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45120</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>45120</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45121</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45121</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45121</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45126</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45127</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45135</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45135</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45140</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45147</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45147</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45147</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45149</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45149</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45149</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45149</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45152</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45154</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>45154</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45154</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45154</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45156</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45156</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45157</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45156</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46961,7 +46961,7 @@
         <v>45159</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45159</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45160</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45160</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47199,7 +47199,7 @@
         <v>45161</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45162</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45163</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45163</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45166</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45166</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45166</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45167</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45167</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45169</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45173</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45173</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45173</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45173</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45175</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45175</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45175</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45175</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45174</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45175</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45175</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45176</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>45177</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45180</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45180</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45182</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45184</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45187</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45187</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45187</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45188</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45188</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45188</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45189</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49227,7 +49227,7 @@
         <v>45189</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45189</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45190</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45190</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45191</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45194</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45196</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45196</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45198</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45198</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>45199</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45198</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45198</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45201</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45201</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45203</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45204</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45204</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45205</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45206</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45206</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45208</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45210</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45214</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>45215</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45217</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45218</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45218</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45221</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45222</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45223</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>45224</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45224</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45224</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45229</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>45233</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45235</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         </is>
       </c>
       <c r="G819" t="n">
-        <v>11.2</v>
+        <v>3.9</v>
       </c>
       <c r="H819" t="n">
         <v>0</v>
@@ -51565,7 +51565,7 @@
         <v>45236</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>45236</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>45236</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51751,7 +51751,7 @@
         <v>45240</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>45239</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51875,7 +51875,7 @@
         <v>45240</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51937,7 +51937,7 @@
         <v>45244</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51992,14 +51992,14 @@
     <row r="827" ht="15" customHeight="1">
       <c r="A827" t="inlineStr">
         <is>
-          <t>A 56826-2023</t>
+          <t>A 57920-2023</t>
         </is>
       </c>
       <c r="B827" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52011,13 +52011,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F827" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="G827" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -52054,14 +52049,14 @@
     <row r="828" ht="15" customHeight="1">
       <c r="A828" t="inlineStr">
         <is>
-          <t>A 57920-2023</t>
+          <t>A 56826-2023</t>
         </is>
       </c>
       <c r="B828" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52073,8 +52068,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="G828" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -52118,7 +52118,7 @@
         <v>45245</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>45245</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52235,14 +52235,14 @@
     <row r="831" ht="15" customHeight="1">
       <c r="A831" t="inlineStr">
         <is>
-          <t>A 57641-2023</t>
+          <t>A 57788-2023</t>
         </is>
       </c>
       <c r="B831" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52254,8 +52254,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G831" t="n">
-        <v>2.6</v>
+        <v>7.7</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -52292,14 +52297,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 57788-2023</t>
+          <t>A 57800-2023</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52317,7 +52322,7 @@
         </is>
       </c>
       <c r="G832" t="n">
-        <v>7.7</v>
+        <v>1.5</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -52354,14 +52359,14 @@
     <row r="833" ht="15" customHeight="1">
       <c r="A833" t="inlineStr">
         <is>
-          <t>A 57800-2023</t>
+          <t>A 57641-2023</t>
         </is>
       </c>
       <c r="B833" s="1" t="n">
-        <v>45247</v>
+        <v>45246</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52373,13 +52378,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F833" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G833" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -52423,7 +52423,7 @@
         <v>45246</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>45250</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>45258</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -564,7 +564,7 @@
         <v>44354</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45114</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>43423</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43402</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>44210</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>43472</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>43664</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>44125</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44026</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>44498</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45177</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>44470</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44854</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44861</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44960</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>43738</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>43738</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>44418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44960</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>45182</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44015</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44139</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44860</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44986</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44987</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>45016</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45191</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45201</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>43427</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>43439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43636</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>43803</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>43888</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>43936</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44082</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44082</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44393</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44393</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44501</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44764</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44817</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44823</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44925</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44985</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45112</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45113</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45113</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45208</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>43339</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>43374</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>43440</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>43445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>43473</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>43493</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>43500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>43500</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>43501</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>43504</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>43504</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>43504</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>43504</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>43507</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>43510</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>43516</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>43517</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>43517</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>43523</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>43531</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>43536</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>43539</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43544</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>43559</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>43585</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>43585</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43585</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>43585</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>43587</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43591</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43601</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>43614</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>43636</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43664</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>43664</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>43664</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43686</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43697</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43700</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43705</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>43707</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>43709</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43738</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43738</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43738</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43739</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>43740</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43748</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>43752</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>43753</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43754</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>43755</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>43760</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>43761</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>43768</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>43768</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>43769</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>43769</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43787</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43787</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43794</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43794</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43795</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43803</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43803</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43803</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>43805</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>43810</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43818</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43833</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43841</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>43843</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>43843</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>43845</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>43852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>43859</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>43888</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>43924</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>43936</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>43936</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>43961</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>43976</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>43980</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43980</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43983</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43987</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43993</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43993</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43993</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44004</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44007</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44014</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44026</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44028</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44029</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44029</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44029</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>44029</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44029</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44050</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>44054</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>44060</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44071</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44078</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44082</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44082</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>44089</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44089</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44089</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44089</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44090</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44090</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44090</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44090</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44096</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44106</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44106</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44106</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44115</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44116</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44117</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44125</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44132</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44132</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44132</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44133</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44134</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44141</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44147</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44147</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44148</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44151</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44151</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44151</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>44152</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>44161</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44163</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44166</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44168</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44170</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44170</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44175</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44186</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44193</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44207</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44210</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44211</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44218</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44218</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44230</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44231</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44231</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44231</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44323</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44328</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44341</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44344</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44344</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44344</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44350</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44350</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>44351</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44356</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44357</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44357</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>44368</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44371</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>44377</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44377</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44377</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>44377</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44377</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44377</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44377</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>44378</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44379</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44379</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44381</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>44382</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44386</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44386</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44386</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>44386</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44391</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44390</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>44391</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44390</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44392</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44393</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44393</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>44399</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>44404</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44407</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44417</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>44418</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44420</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44420</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>44420</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44424</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44426</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44426</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44426</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44428</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44433</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44433</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44438</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44438</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44449</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44449</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44453</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>44455</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44459</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44470</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44470</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>44472</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44473</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44473</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44474</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44476</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44476</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44477</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44477</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44483</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44489</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>44490</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44490</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44496</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44496</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>44496</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44496</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44496</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44497</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44497</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44498</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44498</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44498</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44498</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44498</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>44501</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>44503</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>44503</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>44503</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44505</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44505</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44505</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>44510</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44512</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44516</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44516</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44518</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44519</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44519</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>44519</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44523</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44524</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44525</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44526</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44526</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44526</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44530</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>44531</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44533</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44533</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44551</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>44551</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44585</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44585</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44585</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44586</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44592</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44592</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44594</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44595</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44607</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44615</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44632</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44637</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44642</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44652</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44652</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44662</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44662</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44672</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44674</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44674</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44678</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44681</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44687</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44687</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>44687</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44687</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44687</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44694</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44694</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44694</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44697</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>44698</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44698</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44701</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44708</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44708</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44708</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>44708</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44708</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44708</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>44709</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44711</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44711</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44713</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>44719</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>44722</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>44726</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44726</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44727</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44728</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44728</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>44729</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44740</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>44739</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44741</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44742</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44742</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44744</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44747</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>44747</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>44749</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>44751</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44750</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44750</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44754</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44755</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44755</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44755</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>44755</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44756</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44756</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44757</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44762</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>44761</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>44761</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>44768</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>44770</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44770</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>44774</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>44775</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>44779</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44778</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44779</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44781</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44781</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44783</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44796</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44795</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>44795</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44798</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44799</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44799</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44803</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44803</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44803</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44803</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44803</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44803</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>44806</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44807</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44809</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44809</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44813</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44813</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44813</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44813</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44814</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44816</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44816</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44816</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44816</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44818</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>44818</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44818</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>44818</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44818</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44819</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44820</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44826</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>44826</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44830</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44832</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44834</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44839</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44839</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44846</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44846</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44846</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44847</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44848</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>44847</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>44852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44855</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44858</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44858</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44859</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>44859</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>44860</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44860</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44862</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>44862</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44866</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>44868</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44872</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44872</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44876</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>44879</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>44886</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>44886</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44886</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>44887</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44888</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44888</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44894</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44908</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44908</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>44908</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44908</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>44908</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44908</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>44911</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44911</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>44915</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44917</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44917</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44922</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44925</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>44925</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>44928</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>44929</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44936</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44936</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44936</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44936</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>44936</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>44936</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44936</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44937</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44938</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44938</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>44943</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>44943</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>44943</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44943</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>44950</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44950</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44951</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44952</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>44952</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44952</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44952</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44952</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44952</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44954</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44953</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44958</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44959</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44960</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44960</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44960</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44964</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44966</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44966</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44967</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44967</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44970</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44970</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44970</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44971</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44973</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44973</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44977</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44978</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>44978</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>44977</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>44980</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44984</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44984</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44984</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44985</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44985</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44986</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44986</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44986</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44987</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44988</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>44988</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>44988</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44988</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44988</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44992</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>44993</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>44993</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>44994</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45000</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45005</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45005</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45005</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45009</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45010</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45010</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45010</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45010</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45010</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45010</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45009</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45014</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45014</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>45016</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45030</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>45035</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45036</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45037</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45038</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45040</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45041</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45042</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45042</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45044</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45044</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45048</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45051</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45061</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45068</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45068</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45068</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45068</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45068</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45068</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45072</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45072</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45072</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45077</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45077</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45077</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45077</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>45078</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45078</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45078</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45078</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45078</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45078</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>45078</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45078</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45079</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45078</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45078</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45078</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45079</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45079</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45079</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45084</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45091</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45092</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45092</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45092</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>45092</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45092</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45092</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>45092</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45092</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45093</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45093</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>45093</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45096</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45098</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45098</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45099</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45099</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45099</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45099</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45099</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45099</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45103</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45103</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45103</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45103</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45103</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45103</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45103</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45103</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45103</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45103</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45105</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45107</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45107</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45112</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>45112</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45113</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45114</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45114</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>45114</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45114</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45114</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45113</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45114</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45114</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45114</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45113</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45113</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45113</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45113</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45113</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45114</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45114</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45114</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45114</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45117</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45119</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>45119</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45119</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45119</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45120</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45120</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45120</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>45120</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45121</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45121</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45121</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45126</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45127</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45135</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45135</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45140</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45147</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45147</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45147</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45149</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45149</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45149</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45149</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45152</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45154</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>45154</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45154</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45154</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45156</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45156</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45157</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45156</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46961,7 +46961,7 @@
         <v>45159</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45159</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45160</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45160</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47199,7 +47199,7 @@
         <v>45161</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45162</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45163</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45163</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45166</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45166</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45166</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45167</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45167</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45169</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45173</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45173</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45173</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45173</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45175</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45175</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45175</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45175</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45174</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45175</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45175</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45176</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>45177</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45180</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45180</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45182</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45184</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45187</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45187</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45187</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45188</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45188</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45188</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45189</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49227,7 +49227,7 @@
         <v>45189</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45189</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45190</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45190</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45191</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45194</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45196</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45196</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45198</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45198</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>45199</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45198</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45198</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45201</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45201</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45203</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45204</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45204</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45205</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45206</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45206</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45208</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45210</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45214</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>45215</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45217</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45218</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45218</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45221</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45222</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45223</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>45224</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45224</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45224</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45229</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>45233</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45235</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>45236</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51620,14 +51620,14 @@
     <row r="821" ht="15" customHeight="1">
       <c r="A821" t="inlineStr">
         <is>
-          <t>A 54765-2023</t>
+          <t>A 54746-2023</t>
         </is>
       </c>
       <c r="B821" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51645,7 +51645,7 @@
         </is>
       </c>
       <c r="G821" t="n">
-        <v>18.9</v>
+        <v>4.1</v>
       </c>
       <c r="H821" t="n">
         <v>0</v>
@@ -51682,14 +51682,14 @@
     <row r="822" ht="15" customHeight="1">
       <c r="A822" t="inlineStr">
         <is>
-          <t>A 54746-2023</t>
+          <t>A 54765-2023</t>
         </is>
       </c>
       <c r="B822" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
         </is>
       </c>
       <c r="G822" t="n">
-        <v>4.1</v>
+        <v>18.9</v>
       </c>
       <c r="H822" t="n">
         <v>0</v>
@@ -51751,7 +51751,7 @@
         <v>45240</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>45239</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51875,7 +51875,7 @@
         <v>45240</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51937,7 +51937,7 @@
         <v>45244</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51992,14 +51992,14 @@
     <row r="827" ht="15" customHeight="1">
       <c r="A827" t="inlineStr">
         <is>
-          <t>A 57920-2023</t>
+          <t>A 56826-2023</t>
         </is>
       </c>
       <c r="B827" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52011,8 +52011,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="G827" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -52049,14 +52054,14 @@
     <row r="828" ht="15" customHeight="1">
       <c r="A828" t="inlineStr">
         <is>
-          <t>A 56826-2023</t>
+          <t>A 57920-2023</t>
         </is>
       </c>
       <c r="B828" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52068,13 +52073,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F828" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="G828" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -52111,14 +52111,14 @@
     <row r="829" ht="15" customHeight="1">
       <c r="A829" t="inlineStr">
         <is>
-          <t>A 57307-2023</t>
+          <t>A 57377-2023</t>
         </is>
       </c>
       <c r="B829" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52132,11 +52132,11 @@
       </c>
       <c r="F829" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="G829" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -52173,14 +52173,14 @@
     <row r="830" ht="15" customHeight="1">
       <c r="A830" t="inlineStr">
         <is>
-          <t>A 57377-2023</t>
+          <t>A 57632-2023</t>
         </is>
       </c>
       <c r="B830" s="1" t="n">
-        <v>45245</v>
+        <v>45246</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52192,13 +52192,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F830" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="G830" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -52235,14 +52230,14 @@
     <row r="831" ht="15" customHeight="1">
       <c r="A831" t="inlineStr">
         <is>
-          <t>A 57788-2023</t>
+          <t>A 57641-2023</t>
         </is>
       </c>
       <c r="B831" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52254,13 +52249,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F831" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G831" t="n">
-        <v>7.7</v>
+        <v>2.6</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -52297,14 +52287,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 57800-2023</t>
+          <t>A 57788-2023</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
-        <v>45247</v>
+        <v>45246</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52322,7 +52312,7 @@
         </is>
       </c>
       <c r="G832" t="n">
-        <v>1.5</v>
+        <v>7.7</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -52359,14 +52349,14 @@
     <row r="833" ht="15" customHeight="1">
       <c r="A833" t="inlineStr">
         <is>
-          <t>A 57641-2023</t>
+          <t>A 57800-2023</t>
         </is>
       </c>
       <c r="B833" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52378,8 +52368,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G833" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -52416,14 +52411,14 @@
     <row r="834" ht="15" customHeight="1">
       <c r="A834" t="inlineStr">
         <is>
-          <t>A 57632-2023</t>
+          <t>A 58348-2023</t>
         </is>
       </c>
       <c r="B834" s="1" t="n">
-        <v>45246</v>
+        <v>45250</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52435,8 +52430,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="G834" t="n">
-        <v>2.1</v>
+        <v>7.7</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -52473,14 +52473,14 @@
     <row r="835" ht="15" customHeight="1">
       <c r="A835" t="inlineStr">
         <is>
-          <t>A 58348-2023</t>
+          <t>A 59998-2023</t>
         </is>
       </c>
       <c r="B835" s="1" t="n">
-        <v>45250</v>
+        <v>45258</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52494,11 +52494,11 @@
       </c>
       <c r="F835" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="G835" t="n">
-        <v>7.7</v>
+        <v>32.5</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -52535,14 +52535,14 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>A 59998-2023</t>
+          <t>A 60348-2023</t>
         </is>
       </c>
       <c r="B836" s="1" t="n">
-        <v>45258</v>
+        <v>45257</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52554,13 +52554,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F836" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G836" t="n">
-        <v>32.5</v>
+        <v>0.9</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -564,7 +564,7 @@
         <v>44354</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45114</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>43423</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43402</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>44210</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>43472</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>43664</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>44125</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44026</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>44498</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45177</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>44470</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44854</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44861</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44960</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>43738</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>43738</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>44418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44960</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>45182</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44015</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44139</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44860</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44986</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44987</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>45016</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45191</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45201</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>43427</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>43439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43636</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>43803</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>43888</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>43936</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44082</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44082</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44393</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44393</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44501</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44764</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44817</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44823</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44925</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44985</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45112</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45113</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45113</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45208</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>43339</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>43374</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>43440</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>43445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>43473</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>43493</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>43500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>43500</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>43501</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>43504</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>43504</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>43504</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>43504</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>43507</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>43510</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>43516</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>43517</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>43517</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>43523</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>43531</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>43536</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>43539</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43544</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>43559</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>43585</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>43585</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43585</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>43585</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>43587</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43591</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43601</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>43614</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>43636</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43664</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>43664</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>43664</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43686</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43697</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43700</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43705</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>43707</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>43709</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43738</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43738</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43738</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43739</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>43740</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43748</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>43752</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>43753</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43754</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>43755</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>43760</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>43761</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>43768</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>43768</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>43769</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>43769</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43787</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43787</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43794</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43794</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43795</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43803</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43803</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43803</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>43805</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>43810</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43818</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43833</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43841</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>43843</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>43843</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>43845</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>43852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>43859</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>43888</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>43924</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>43936</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>43936</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>43961</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>43976</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>43980</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43980</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43983</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43987</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43993</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43993</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43993</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44004</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44007</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44014</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44026</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44028</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44029</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44029</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44029</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>44029</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44029</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44050</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>44054</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>44060</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44071</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44078</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44082</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44082</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>44089</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44089</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44089</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44089</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44090</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44090</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44090</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44090</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44096</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44106</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44106</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44106</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44115</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44116</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44117</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44125</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44132</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44132</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44132</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44133</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44134</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44141</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44147</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44147</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44148</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44151</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44151</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44151</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>44152</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>44161</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44163</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44166</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44168</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44170</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44170</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44175</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44186</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44193</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44207</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44210</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44211</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44218</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44218</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44230</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44231</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44231</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44231</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44323</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44328</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44341</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44344</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44344</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44344</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44350</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44350</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>44351</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44356</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44357</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44357</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>44368</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44371</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>44377</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44377</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44377</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>44377</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44377</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44377</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44377</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>44378</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44379</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44379</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44381</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>44382</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44386</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44386</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44386</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>44386</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44391</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44390</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>44391</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44390</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44392</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44393</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44393</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>44399</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>44404</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44407</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44417</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>44418</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44420</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44420</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>44420</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44424</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44426</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44426</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44426</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44428</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44433</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44433</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44438</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44438</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44449</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44449</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44453</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>44455</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44459</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44470</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44470</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>44472</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44473</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44473</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44474</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44476</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44476</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44477</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44477</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44483</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44489</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>44490</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44490</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44496</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44496</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>44496</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44496</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44496</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44497</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44497</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44498</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44498</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44498</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44498</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44498</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>44501</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>44503</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>44503</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>44503</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44505</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44505</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44505</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>44510</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44512</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44516</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44516</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44518</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44519</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44519</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>44519</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44523</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44524</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44525</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44526</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44526</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44526</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44530</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>44531</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44533</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44533</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44551</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>44551</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44585</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44585</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44585</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44586</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44592</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44592</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44594</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44595</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44607</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44615</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44632</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44637</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44642</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44652</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44652</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44662</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44662</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44672</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44674</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44674</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44678</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44681</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44687</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44687</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>44687</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44687</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44687</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44694</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44694</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44694</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44697</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>44698</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44698</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44701</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44708</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44708</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44708</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>44708</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44708</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44708</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>44709</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44711</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44711</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44713</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>44719</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>44722</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>44726</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44726</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44727</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44728</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44728</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>44729</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44740</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>44739</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44741</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44742</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44742</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44744</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44747</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>44747</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>44749</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>44751</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44750</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44750</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44754</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44755</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44755</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44755</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>44755</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44756</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44756</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44757</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44762</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>44761</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>44761</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>44768</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>44770</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44770</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>44774</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>44775</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>44779</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44778</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44779</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44781</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44781</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44783</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44796</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44795</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>44795</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44798</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44799</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44799</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44803</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44803</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44803</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44803</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44803</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44803</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>44806</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44807</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44809</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44809</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44813</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44813</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44813</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44813</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44814</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44816</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44816</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44816</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44816</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44818</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>44818</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44818</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>44818</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44818</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44819</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44820</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44826</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>44826</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44830</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44832</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44834</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44839</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44839</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44846</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44846</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44846</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44847</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44848</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>44847</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>44852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44855</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44858</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44858</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44859</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>44859</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>44860</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44860</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44862</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>44862</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44866</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>44868</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44872</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44872</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44876</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>44879</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>44886</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>44886</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44886</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>44887</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44888</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44888</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44894</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44908</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44908</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>44908</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44908</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>44908</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44908</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>44911</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44911</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>44915</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44917</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44917</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44922</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44925</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>44925</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>44928</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>44929</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44936</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44936</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44936</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44936</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>44936</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>44936</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44936</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44937</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44938</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44938</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>44943</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>44943</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>44943</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44943</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>44950</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44950</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44951</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44952</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>44952</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44952</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44952</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44952</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44952</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44954</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44953</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44958</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44959</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44960</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44960</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44960</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44964</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44966</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44966</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44967</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44967</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44970</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44970</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44970</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44971</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44973</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44973</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44977</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44978</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>44978</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>44977</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>44980</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44984</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44984</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44984</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44985</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44985</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44986</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44986</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44986</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44987</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44988</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>44988</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>44988</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44988</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44988</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44992</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>44993</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>44993</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>44994</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45000</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45005</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45005</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45005</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45009</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45010</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45010</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45010</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45010</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45010</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45010</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45009</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45014</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45014</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>45016</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45030</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>45035</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45036</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45037</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45038</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45040</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45041</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45042</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45042</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45044</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45044</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45048</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45051</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45061</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45068</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45068</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45068</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45068</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45068</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45068</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45072</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45072</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45072</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45077</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45077</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45077</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45077</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>45078</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45078</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45078</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45078</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45078</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45078</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>45078</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45078</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45079</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45078</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45078</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45078</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45079</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45079</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45079</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45084</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45091</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45092</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45092</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45092</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>45092</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45092</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45092</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>45092</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45092</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45093</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45093</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>45093</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45096</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45098</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45098</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45099</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45099</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45099</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45099</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45099</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45099</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45103</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45103</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45103</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45103</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45103</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45103</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45103</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45103</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45103</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45103</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45105</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45107</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45107</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45112</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>45112</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45113</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45114</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45114</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>45114</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45114</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45114</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45113</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45114</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45114</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45114</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45113</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45113</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45113</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45113</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45113</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45114</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45114</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45114</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45114</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45117</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45119</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>45119</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45119</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45119</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45120</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45120</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45120</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>45120</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45121</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45121</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45121</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45126</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45127</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45135</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45135</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45140</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45147</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45147</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45147</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45149</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45149</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45149</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45149</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45152</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45154</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>45154</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45154</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45154</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45156</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45156</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45157</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45156</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46961,7 +46961,7 @@
         <v>45159</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45159</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45160</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45160</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47199,7 +47199,7 @@
         <v>45161</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45162</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45163</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45163</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45166</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45166</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45166</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45167</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45167</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45169</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45173</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45173</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45173</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45173</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45175</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45175</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45175</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45175</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45174</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45175</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45175</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45176</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>45177</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45180</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45180</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45182</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45184</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45187</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45187</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45187</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45188</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45188</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45188</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45189</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49227,7 +49227,7 @@
         <v>45189</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45189</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45190</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45190</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45191</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45194</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45196</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45196</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45198</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45198</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>45199</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45198</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45198</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45201</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45201</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45203</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45204</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45204</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45205</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45206</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45206</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45208</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45210</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45214</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>45215</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45217</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45218</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45218</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45221</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45222</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45223</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>45224</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45224</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45224</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45229</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>45233</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45235</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>45236</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51620,14 +51620,14 @@
     <row r="821" ht="15" customHeight="1">
       <c r="A821" t="inlineStr">
         <is>
-          <t>A 54746-2023</t>
+          <t>A 54765-2023</t>
         </is>
       </c>
       <c r="B821" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51645,7 +51645,7 @@
         </is>
       </c>
       <c r="G821" t="n">
-        <v>4.1</v>
+        <v>18.9</v>
       </c>
       <c r="H821" t="n">
         <v>0</v>
@@ -51682,14 +51682,14 @@
     <row r="822" ht="15" customHeight="1">
       <c r="A822" t="inlineStr">
         <is>
-          <t>A 54765-2023</t>
+          <t>A 54746-2023</t>
         </is>
       </c>
       <c r="B822" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
         </is>
       </c>
       <c r="G822" t="n">
-        <v>18.9</v>
+        <v>4.1</v>
       </c>
       <c r="H822" t="n">
         <v>0</v>
@@ -51744,14 +51744,14 @@
     <row r="823" ht="15" customHeight="1">
       <c r="A823" t="inlineStr">
         <is>
-          <t>A 55920-2023</t>
+          <t>A 56981-2023</t>
         </is>
       </c>
       <c r="B823" s="1" t="n">
-        <v>45240</v>
+        <v>45239</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51765,11 +51765,11 @@
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="G823" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -51806,14 +51806,14 @@
     <row r="824" ht="15" customHeight="1">
       <c r="A824" t="inlineStr">
         <is>
-          <t>A 56981-2023</t>
+          <t>A 55920-2023</t>
         </is>
       </c>
       <c r="B824" s="1" t="n">
-        <v>45239</v>
+        <v>45240</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51827,11 +51827,11 @@
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="G824" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -51875,7 +51875,7 @@
         <v>45240</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51930,14 +51930,14 @@
     <row r="826" ht="15" customHeight="1">
       <c r="A826" t="inlineStr">
         <is>
-          <t>A 56961-2023</t>
+          <t>A 56826-2023</t>
         </is>
       </c>
       <c r="B826" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51951,11 +51951,11 @@
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="G826" t="n">
-        <v>10.8</v>
+        <v>2.5</v>
       </c>
       <c r="H826" t="n">
         <v>0</v>
@@ -51992,14 +51992,14 @@
     <row r="827" ht="15" customHeight="1">
       <c r="A827" t="inlineStr">
         <is>
-          <t>A 56826-2023</t>
+          <t>A 56961-2023</t>
         </is>
       </c>
       <c r="B827" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52013,11 +52013,11 @@
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="G827" t="n">
-        <v>2.5</v>
+        <v>10.8</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -52061,7 +52061,7 @@
         <v>45244</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>45245</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52173,14 +52173,14 @@
     <row r="830" ht="15" customHeight="1">
       <c r="A830" t="inlineStr">
         <is>
-          <t>A 57632-2023</t>
+          <t>A 57788-2023</t>
         </is>
       </c>
       <c r="B830" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52192,8 +52192,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G830" t="n">
-        <v>2.1</v>
+        <v>7.7</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -52230,14 +52235,14 @@
     <row r="831" ht="15" customHeight="1">
       <c r="A831" t="inlineStr">
         <is>
-          <t>A 57641-2023</t>
+          <t>A 57800-2023</t>
         </is>
       </c>
       <c r="B831" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52249,8 +52254,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G831" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -52287,14 +52297,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 57788-2023</t>
+          <t>A 57641-2023</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52306,13 +52316,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F832" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G832" t="n">
-        <v>7.7</v>
+        <v>2.6</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -52349,14 +52354,14 @@
     <row r="833" ht="15" customHeight="1">
       <c r="A833" t="inlineStr">
         <is>
-          <t>A 57800-2023</t>
+          <t>A 57632-2023</t>
         </is>
       </c>
       <c r="B833" s="1" t="n">
-        <v>45247</v>
+        <v>45246</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52368,13 +52373,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F833" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G833" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -52418,7 +52418,7 @@
         <v>45250</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>45258</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>45257</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -564,7 +564,7 @@
         <v>44354</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45114</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>43423</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43402</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>44210</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>43472</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>43664</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>44125</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44026</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>44498</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45177</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>44470</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44854</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44861</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44960</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>43738</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>43738</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>44418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44960</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>45182</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44015</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44139</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44860</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44986</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44987</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>45016</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45191</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45201</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>43427</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>43439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43636</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>43803</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>43888</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>43936</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44082</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44082</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44393</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44393</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44501</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44764</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44817</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44823</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44925</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44985</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45112</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45113</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45113</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45208</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>43339</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>43374</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>43440</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>43445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>43473</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>43493</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>43500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>43500</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>43501</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>43504</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>43504</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>43504</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>43504</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>43507</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>43510</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>43516</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>43517</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>43517</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>43523</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>43531</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>43536</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>43539</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43544</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>43559</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>43585</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>43585</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43585</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>43585</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>43587</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43591</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43601</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>43614</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>43636</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43664</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>43664</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>43664</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43686</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43697</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43700</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43705</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>43707</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>43709</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43738</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43738</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43738</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43739</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>43740</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43748</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>43752</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>43753</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43754</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>43755</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>43760</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>43761</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>43768</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>43768</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>43769</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>43769</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43787</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43787</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43794</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43794</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43795</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43803</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43803</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43803</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>43805</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>43810</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43818</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43833</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43841</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>43843</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>43843</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>43845</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>43852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>43859</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>43888</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>43924</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>43936</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>43936</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>43961</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>43976</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>43980</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43980</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43983</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43987</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43993</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43993</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43993</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44004</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44007</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44014</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44026</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44028</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44029</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44029</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44029</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>44029</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44029</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44050</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>44054</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>44060</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44071</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44078</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44082</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44082</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>44089</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44089</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44089</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44089</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44090</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44090</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44090</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44090</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44096</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44106</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44106</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44106</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44115</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44116</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44117</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44125</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44132</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44132</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44132</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44133</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44134</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44141</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44147</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44147</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44148</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44151</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44151</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44151</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>44152</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>44161</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44163</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44166</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44168</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44170</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44170</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44175</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44186</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44193</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44207</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44210</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44211</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44218</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44218</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44230</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44231</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44231</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44231</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44323</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44328</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44341</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44344</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44344</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44344</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44350</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44350</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>44351</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44356</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44357</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44357</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>44368</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44371</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>44377</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44377</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44377</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>44377</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44377</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44377</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44377</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>44378</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44379</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44379</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44381</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>44382</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44386</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44386</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44386</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>44386</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44391</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44390</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>44391</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44390</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44392</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44393</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44393</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>44399</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>44404</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44407</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44417</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>44418</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44420</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44420</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>44420</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44424</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44426</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44426</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44426</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44428</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44433</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44433</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44438</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44438</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44449</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44449</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44453</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>44455</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44459</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44470</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44470</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>44472</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44473</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44473</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44474</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44476</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44476</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44477</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44477</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44483</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44489</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>44490</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44490</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44496</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44496</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>44496</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44496</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44496</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44497</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44497</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44498</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44498</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44498</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44498</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44498</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>44501</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>44503</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>44503</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>44503</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44505</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44505</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44505</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>44510</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44512</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44516</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44516</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44518</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44519</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44519</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>44519</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44523</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44524</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44525</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44526</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44526</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44526</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44530</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>44531</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44533</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44533</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44551</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>44551</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44585</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44585</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44585</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44586</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44592</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44592</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44594</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44595</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44607</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44615</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44632</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44637</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44642</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44652</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44652</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44662</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44662</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44672</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44674</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44674</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44678</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44681</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44687</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44687</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>44687</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44687</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44687</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44694</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44694</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44694</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44697</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>44698</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44698</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44701</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44708</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44708</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44708</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>44708</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44708</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44708</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>44709</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44711</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44711</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44713</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>44719</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>44722</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>44726</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44726</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44727</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44728</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44728</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>44729</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44740</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>44739</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44741</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44742</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44742</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44744</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44747</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>44747</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>44749</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>44751</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44750</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44750</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44754</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44755</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44755</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44755</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>44755</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44756</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44756</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44757</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44762</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>44761</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>44761</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>44768</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>44770</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44770</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>44774</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>44775</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>44779</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44778</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44779</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44781</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44781</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44783</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44796</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44795</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>44795</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44798</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44799</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44799</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44803</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44803</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44803</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44803</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44803</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44803</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>44806</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44807</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44809</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44809</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44813</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44813</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44813</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44813</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44814</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44816</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44816</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44816</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44816</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44818</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>44818</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44818</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>44818</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44818</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44819</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44820</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44826</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>44826</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44830</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44832</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44834</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44839</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44839</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44846</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44846</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44846</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44847</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44848</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>44847</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>44852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44855</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44858</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44858</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44859</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>44859</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>44860</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44860</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44862</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>44862</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44866</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>44868</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44872</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44872</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44876</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>44879</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>44886</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>44886</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44886</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>44887</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44888</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44888</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44894</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44908</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44908</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>44908</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44908</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>44908</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44908</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>44911</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44911</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>44915</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44917</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44917</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44922</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44925</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>44925</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>44928</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>44929</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44936</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44936</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44936</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44936</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>44936</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>44936</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44936</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44937</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44938</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44938</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>44943</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>44943</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>44943</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44943</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>44950</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44950</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44951</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44952</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>44952</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44952</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44952</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44952</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44952</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44954</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44953</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44958</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44959</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44960</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44960</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44960</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44964</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44966</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44966</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44967</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44967</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44970</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44970</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44970</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44971</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44973</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44973</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44977</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44978</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>44978</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>44977</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>44980</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44984</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44984</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44984</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44985</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44985</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44986</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44986</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44986</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44987</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44988</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>44988</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>44988</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44988</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44988</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44992</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>44993</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>44993</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>44994</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45000</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45005</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45005</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45005</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45009</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45010</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45010</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45010</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45010</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45010</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45010</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45009</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45014</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45014</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>45016</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45030</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>45035</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45036</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45037</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45038</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45040</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45041</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45042</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45042</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45044</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45044</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45048</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45051</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45061</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45068</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45068</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45068</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45068</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45068</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45068</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45072</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45072</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45072</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45077</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45077</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45077</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45077</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>45078</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45078</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45078</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45078</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45078</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45078</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>45078</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45078</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45079</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45078</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45078</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45078</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45079</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45079</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45079</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45084</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45091</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45092</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45092</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45092</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>45092</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45092</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45092</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>45092</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45092</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45093</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45093</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>45093</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45096</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45098</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45098</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45099</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45099</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45099</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45099</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45099</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45099</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45103</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45103</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45103</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45103</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45103</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45103</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45103</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45103</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45103</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45103</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45105</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45107</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45107</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45112</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>45112</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45113</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45114</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45114</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>45114</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45114</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45114</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45113</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45114</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45114</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45114</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45113</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45113</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45113</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45113</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45113</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45114</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45114</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45114</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45114</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45117</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45119</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>45119</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45119</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45119</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45120</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45120</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45120</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>45120</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45121</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45121</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45121</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45126</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45127</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45135</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45135</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45140</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45147</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45147</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45147</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45149</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45149</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45149</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45149</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45152</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45154</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>45154</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45154</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45154</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45156</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45156</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45157</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45156</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46961,7 +46961,7 @@
         <v>45159</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45159</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45160</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45160</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47199,7 +47199,7 @@
         <v>45161</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45162</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45163</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45163</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45166</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45166</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45166</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45167</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45167</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45169</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45173</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45173</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45173</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45173</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45175</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45175</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45175</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45175</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45174</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45175</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45175</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45176</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>45177</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45180</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45180</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45182</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45184</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45187</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45187</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45187</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45188</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45188</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45188</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45189</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49227,7 +49227,7 @@
         <v>45189</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45189</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45190</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45190</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45191</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45194</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45196</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45196</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45198</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45198</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>45199</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45198</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45198</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45201</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45201</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45203</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45204</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45204</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45205</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45206</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45206</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45208</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45210</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45214</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>45215</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45217</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45218</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45218</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45221</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45222</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45223</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>45224</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45224</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45224</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45229</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>45233</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45235</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51558,14 +51558,14 @@
     <row r="820" ht="15" customHeight="1">
       <c r="A820" t="inlineStr">
         <is>
-          <t>A 54741-2023</t>
+          <t>A 54746-2023</t>
         </is>
       </c>
       <c r="B820" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51583,7 +51583,7 @@
         </is>
       </c>
       <c r="G820" t="n">
-        <v>23.4</v>
+        <v>4.1</v>
       </c>
       <c r="H820" t="n">
         <v>0</v>
@@ -51620,14 +51620,14 @@
     <row r="821" ht="15" customHeight="1">
       <c r="A821" t="inlineStr">
         <is>
-          <t>A 54765-2023</t>
+          <t>A 54741-2023</t>
         </is>
       </c>
       <c r="B821" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51645,7 +51645,7 @@
         </is>
       </c>
       <c r="G821" t="n">
-        <v>18.9</v>
+        <v>23.4</v>
       </c>
       <c r="H821" t="n">
         <v>0</v>
@@ -51682,14 +51682,14 @@
     <row r="822" ht="15" customHeight="1">
       <c r="A822" t="inlineStr">
         <is>
-          <t>A 54746-2023</t>
+          <t>A 54765-2023</t>
         </is>
       </c>
       <c r="B822" s="1" t="n">
         <v>45236</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
         </is>
       </c>
       <c r="G822" t="n">
-        <v>4.1</v>
+        <v>18.9</v>
       </c>
       <c r="H822" t="n">
         <v>0</v>
@@ -51744,14 +51744,14 @@
     <row r="823" ht="15" customHeight="1">
       <c r="A823" t="inlineStr">
         <is>
-          <t>A 56981-2023</t>
+          <t>A 55920-2023</t>
         </is>
       </c>
       <c r="B823" s="1" t="n">
-        <v>45239</v>
+        <v>45240</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51765,11 +51765,11 @@
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="G823" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -51806,14 +51806,14 @@
     <row r="824" ht="15" customHeight="1">
       <c r="A824" t="inlineStr">
         <is>
-          <t>A 55920-2023</t>
+          <t>A 56981-2023</t>
         </is>
       </c>
       <c r="B824" s="1" t="n">
-        <v>45240</v>
+        <v>45239</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51827,11 +51827,11 @@
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="G824" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -51875,7 +51875,7 @@
         <v>45240</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51937,7 +51937,7 @@
         <v>45244</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51999,7 +51999,7 @@
         <v>45244</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52061,7 +52061,7 @@
         <v>45244</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>45245</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52173,14 +52173,14 @@
     <row r="830" ht="15" customHeight="1">
       <c r="A830" t="inlineStr">
         <is>
-          <t>A 57788-2023</t>
+          <t>A 57632-2023</t>
         </is>
       </c>
       <c r="B830" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52192,13 +52192,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F830" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G830" t="n">
-        <v>7.7</v>
+        <v>2.1</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -52235,14 +52230,14 @@
     <row r="831" ht="15" customHeight="1">
       <c r="A831" t="inlineStr">
         <is>
-          <t>A 57800-2023</t>
+          <t>A 57788-2023</t>
         </is>
       </c>
       <c r="B831" s="1" t="n">
-        <v>45247</v>
+        <v>45246</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52260,7 +52255,7 @@
         </is>
       </c>
       <c r="G831" t="n">
-        <v>1.5</v>
+        <v>7.7</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -52297,14 +52292,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 57641-2023</t>
+          <t>A 57800-2023</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52316,8 +52311,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G832" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -52354,14 +52354,14 @@
     <row r="833" ht="15" customHeight="1">
       <c r="A833" t="inlineStr">
         <is>
-          <t>A 57632-2023</t>
+          <t>A 57641-2023</t>
         </is>
       </c>
       <c r="B833" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         </is>
       </c>
       <c r="G833" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -52418,7 +52418,7 @@
         <v>45250</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52477,10 +52477,10 @@
         </is>
       </c>
       <c r="B835" s="1" t="n">
-        <v>45258</v>
+        <v>45257</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>45257</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -564,7 +564,7 @@
         <v>44354</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45114</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>43423</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43402</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>44210</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>43472</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>43664</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>44125</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44026</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>44498</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45177</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>44470</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44854</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44861</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44960</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>43738</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>43738</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>44418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44960</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>45182</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44015</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44139</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44860</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44986</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44987</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>45016</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45191</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45201</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>43427</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>43439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43636</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>43803</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>43888</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>43936</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44082</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44082</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44393</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44393</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44501</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44764</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44817</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44823</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44925</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44985</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45112</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45113</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45113</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45208</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>43339</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>43374</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>43440</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>43445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>43473</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>43493</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>43500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>43500</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>43501</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>43504</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>43504</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>43504</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>43504</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>43507</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>43510</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>43516</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>43517</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>43517</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>43523</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>43531</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>43536</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>43539</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43544</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>43559</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>43585</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>43585</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43585</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>43585</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>43587</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43591</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43601</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>43614</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>43636</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43664</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>43664</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>43664</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43686</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43697</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43700</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43705</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>43707</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>43709</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43738</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43738</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43738</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43739</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>43740</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43748</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>43752</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>43753</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43754</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>43755</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>43760</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>43761</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>43768</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>43768</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>43769</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>43769</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43787</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43787</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43794</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43794</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43795</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43803</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43803</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43803</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>43805</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>43810</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43818</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43833</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43841</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>43843</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>43843</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>43845</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>43852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>43859</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>43888</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>43924</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>43936</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>43936</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>43961</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>43976</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>43980</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43980</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43983</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43987</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43993</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43993</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43993</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44004</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44007</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44014</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44026</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44028</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44029</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44029</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44029</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>44029</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44029</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44050</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>44054</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>44060</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44071</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44078</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44082</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44082</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>44089</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44089</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44089</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44089</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44090</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44090</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44090</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44090</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44096</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44106</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44106</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44106</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44115</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44116</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44117</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44125</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44132</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44132</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44132</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44133</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44134</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44141</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44147</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44147</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44148</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44151</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44151</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44151</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>44152</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>44161</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44163</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44166</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44168</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44170</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44170</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44175</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44186</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44193</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44207</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44210</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44211</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44218</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44218</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44230</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44231</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44231</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44231</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44323</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44328</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44341</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44344</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44344</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44344</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44350</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44350</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>44351</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44356</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44357</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44357</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>44368</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44371</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>44377</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44377</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44377</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>44377</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44377</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44377</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44377</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>44378</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44379</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44379</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44381</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>44382</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44386</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44386</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44386</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>44386</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44391</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44390</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>44391</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44390</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44392</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44393</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44393</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>44399</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>44404</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44407</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44417</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>44418</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44420</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44420</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>44420</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44424</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44426</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44426</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44426</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44428</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44433</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44433</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44438</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44438</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44449</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44449</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44453</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>44455</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44459</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44470</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44470</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>44472</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44473</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44473</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44474</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44476</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44476</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44477</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44477</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44483</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44489</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>44490</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44490</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44496</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44496</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>44496</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44496</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44496</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44497</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44497</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44498</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44498</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44498</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44498</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44498</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>44501</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>44503</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>44503</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>44503</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44505</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44505</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44505</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>44510</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44512</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44516</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44516</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44518</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44519</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44519</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>44519</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44523</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44524</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44525</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44526</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44526</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44526</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44530</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>44531</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44533</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44533</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44551</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>44551</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44585</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44585</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44585</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44586</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44592</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44592</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44594</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44595</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44607</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44615</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44632</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44637</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44642</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44652</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44652</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44662</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44662</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44672</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44674</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44674</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44678</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44681</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44687</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44687</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>44687</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44687</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44687</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44694</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44694</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44694</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44697</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>44698</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44698</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44701</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44708</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44708</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44708</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>44708</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44708</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44708</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>44709</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44711</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44711</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44713</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>44719</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>44722</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>44726</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44726</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44727</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44728</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44728</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>44729</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44740</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>44739</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44741</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44742</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44742</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44744</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44747</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>44747</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>44749</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>44751</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44750</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44750</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44754</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44755</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44755</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44755</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>44755</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44756</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44756</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44757</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44762</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>44761</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>44761</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>44768</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>44770</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44770</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>44774</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>44775</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>44779</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44778</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44779</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44781</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44781</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44783</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44796</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44795</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>44795</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44798</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44799</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44799</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44803</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44803</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44803</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44803</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44803</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44803</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>44806</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44807</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44809</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44809</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44813</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44813</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44813</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44813</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44814</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44816</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44816</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44816</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44816</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44818</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>44818</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44818</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>44818</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44818</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44819</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44820</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44826</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>44826</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44830</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44832</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44834</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44839</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44839</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44846</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44846</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44846</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44847</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44848</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>44847</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>44852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44855</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44858</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44858</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44859</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>44859</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>44860</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44860</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44862</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>44862</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44866</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>44868</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44872</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44872</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44876</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>44879</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>44886</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>44886</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44886</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>44887</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44888</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44888</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44894</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44908</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44908</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>44908</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44908</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>44908</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44908</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>44911</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44911</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>44915</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44917</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44917</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44922</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44925</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>44925</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>44928</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>44929</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44936</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44936</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44936</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44936</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>44936</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>44936</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44936</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44937</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44938</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44938</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>44943</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>44943</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>44943</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44943</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>44950</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44950</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44951</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44952</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>44952</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44952</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44952</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44952</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44952</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44954</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44953</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44958</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44959</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44960</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44960</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44960</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44964</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44966</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44966</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44967</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44967</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44970</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44970</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44970</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44971</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44973</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44973</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44977</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44978</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>44978</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>44977</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>44980</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44984</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44984</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44984</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44985</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44985</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44986</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44986</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44986</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44987</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44988</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>44988</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>44988</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44988</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44988</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44992</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>44993</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>44993</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>44994</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45000</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45005</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45005</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45005</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45009</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45010</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45010</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45010</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45010</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45010</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45010</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45009</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45014</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45014</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>45016</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45030</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>45035</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45036</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45037</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45038</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45040</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45041</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45042</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45042</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45044</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45044</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45048</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45051</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45061</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45068</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45068</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45068</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45068</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45068</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45068</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45072</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45072</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45072</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45077</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45077</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45077</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45077</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>45078</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45078</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45078</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45078</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45078</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45078</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>45078</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45078</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45079</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45078</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45078</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45078</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45079</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45079</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45079</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45084</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45091</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45092</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45092</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45092</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>45092</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45092</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45092</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>45092</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45092</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45093</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45093</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>45093</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45096</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45098</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45098</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45099</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45099</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45099</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45099</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45099</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45099</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45103</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45103</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45103</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45103</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45103</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45103</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45103</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45103</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45103</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45103</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45105</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45107</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45107</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45112</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>45112</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45113</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45114</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45114</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>45114</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45114</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45114</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45113</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45114</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45114</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45114</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45113</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45113</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45113</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45113</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45113</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45114</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45114</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45114</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45114</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45117</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45119</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>45119</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45119</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45119</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45120</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45120</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45120</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>45120</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45121</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45121</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45121</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45126</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45127</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45135</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45135</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45140</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45147</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45147</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45147</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45149</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45149</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45149</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45149</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45152</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45154</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>45154</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45154</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45154</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45156</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45156</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45157</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45156</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46961,7 +46961,7 @@
         <v>45159</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45159</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45160</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45160</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47199,7 +47199,7 @@
         <v>45161</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45162</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45163</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45163</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45166</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45166</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45166</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45167</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45167</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45169</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45173</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45173</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45173</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45173</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45175</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45175</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45175</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45175</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45174</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45175</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45175</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45176</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>45177</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45180</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45180</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45182</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45184</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45187</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45187</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45187</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45188</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45188</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45188</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45189</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49227,7 +49227,7 @@
         <v>45189</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45189</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45190</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45190</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45191</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45194</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45196</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45196</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45198</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45198</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>45199</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45198</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45198</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45201</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45201</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45203</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45204</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45204</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45205</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45206</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45206</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45208</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45210</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45214</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>45215</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45217</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45218</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45218</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45221</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45222</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45223</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>45224</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45224</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45224</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45229</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>45233</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45235</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>45236</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>45236</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>45236</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51744,14 +51744,14 @@
     <row r="823" ht="15" customHeight="1">
       <c r="A823" t="inlineStr">
         <is>
-          <t>A 55920-2023</t>
+          <t>A 56981-2023</t>
         </is>
       </c>
       <c r="B823" s="1" t="n">
-        <v>45240</v>
+        <v>45239</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51765,11 +51765,11 @@
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="G823" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -51806,14 +51806,14 @@
     <row r="824" ht="15" customHeight="1">
       <c r="A824" t="inlineStr">
         <is>
-          <t>A 56981-2023</t>
+          <t>A 55920-2023</t>
         </is>
       </c>
       <c r="B824" s="1" t="n">
-        <v>45239</v>
+        <v>45240</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51827,11 +51827,11 @@
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="G824" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -51875,7 +51875,7 @@
         <v>45240</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51930,14 +51930,14 @@
     <row r="826" ht="15" customHeight="1">
       <c r="A826" t="inlineStr">
         <is>
-          <t>A 56826-2023</t>
+          <t>A 56961-2023</t>
         </is>
       </c>
       <c r="B826" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51951,11 +51951,11 @@
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="G826" t="n">
-        <v>2.5</v>
+        <v>10.8</v>
       </c>
       <c r="H826" t="n">
         <v>0</v>
@@ -51992,14 +51992,14 @@
     <row r="827" ht="15" customHeight="1">
       <c r="A827" t="inlineStr">
         <is>
-          <t>A 56961-2023</t>
+          <t>A 57920-2023</t>
         </is>
       </c>
       <c r="B827" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52011,13 +52011,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F827" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="G827" t="n">
-        <v>10.8</v>
+        <v>1.2</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -52054,14 +52049,14 @@
     <row r="828" ht="15" customHeight="1">
       <c r="A828" t="inlineStr">
         <is>
-          <t>A 57920-2023</t>
+          <t>A 56826-2023</t>
         </is>
       </c>
       <c r="B828" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52073,8 +52068,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="G828" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -52118,7 +52118,7 @@
         <v>45245</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52173,14 +52173,14 @@
     <row r="830" ht="15" customHeight="1">
       <c r="A830" t="inlineStr">
         <is>
-          <t>A 57632-2023</t>
+          <t>A 57641-2023</t>
         </is>
       </c>
       <c r="B830" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
         </is>
       </c>
       <c r="G830" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -52230,14 +52230,14 @@
     <row r="831" ht="15" customHeight="1">
       <c r="A831" t="inlineStr">
         <is>
-          <t>A 57788-2023</t>
+          <t>A 57632-2023</t>
         </is>
       </c>
       <c r="B831" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52249,13 +52249,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F831" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G831" t="n">
-        <v>7.7</v>
+        <v>2.1</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -52292,14 +52287,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 57800-2023</t>
+          <t>A 57788-2023</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
-        <v>45247</v>
+        <v>45246</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52317,7 +52312,7 @@
         </is>
       </c>
       <c r="G832" t="n">
-        <v>1.5</v>
+        <v>7.7</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -52354,14 +52349,14 @@
     <row r="833" ht="15" customHeight="1">
       <c r="A833" t="inlineStr">
         <is>
-          <t>A 57641-2023</t>
+          <t>A 57800-2023</t>
         </is>
       </c>
       <c r="B833" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52373,8 +52368,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G833" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -52418,7 +52418,7 @@
         <v>45250</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>45257</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>45257</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -564,7 +564,7 @@
         <v>44354</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45114</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>43423</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43402</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>44210</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>43472</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>43664</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>44125</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44026</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>44498</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45177</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>44470</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44854</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44861</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44960</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>43738</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>43738</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>44418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44960</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>45182</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44015</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44139</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44860</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44986</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44987</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>45016</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45191</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45201</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>43427</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>43439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43636</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>43803</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>43888</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>43936</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44082</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44082</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44393</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44393</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44501</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44764</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44817</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44823</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44925</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44985</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45112</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45113</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45113</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45208</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>43339</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>43374</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>43440</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>43445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>43473</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>43493</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>43500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>43500</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>43501</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>43504</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>43504</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>43504</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>43504</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>43507</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>43510</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>43516</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>43517</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>43517</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>43523</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>43531</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>43536</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>43539</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43544</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>43559</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>43585</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>43585</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43585</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>43585</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>43587</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43591</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43601</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>43614</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>43636</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43664</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>43664</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>43664</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43686</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43697</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43700</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43705</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>43707</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>43709</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43738</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43738</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43738</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43739</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>43740</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43748</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>43752</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>43753</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43754</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>43755</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>43760</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>43761</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>43768</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>43768</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>43769</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>43769</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43787</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43787</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43794</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43794</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43795</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43803</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43803</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43803</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>43805</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>43810</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43818</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43833</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43841</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>43843</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>43843</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>43845</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>43852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>43859</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>43888</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>43924</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>43936</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>43936</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>43961</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>43976</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>43980</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43980</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43983</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43987</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43993</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43993</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43993</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44004</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44007</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44014</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44026</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44028</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44029</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44029</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44029</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>44029</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44029</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44050</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>44054</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>44060</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44071</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44078</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44082</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44082</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>44089</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44089</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44089</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44089</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44090</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44090</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44090</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44090</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44096</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44106</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44106</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44106</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44115</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44116</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44117</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44125</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44132</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44132</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44132</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44133</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44134</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44141</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44147</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44147</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44148</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44151</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44151</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44151</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>44152</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>44161</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44163</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44166</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44168</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44170</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44170</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44175</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44186</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44193</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44207</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44210</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44211</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44218</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44218</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44230</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44231</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44231</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44231</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44323</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44328</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44341</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44344</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44344</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44344</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44350</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44350</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>44351</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44356</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44357</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44357</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>44368</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44371</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>44377</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44377</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44377</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>44377</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44377</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44377</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44377</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>44378</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44379</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44379</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44381</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>44382</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44386</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44386</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44386</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>44386</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44391</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44390</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>44391</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44390</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44392</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44393</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44393</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>44399</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>44404</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44407</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44417</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>44418</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44420</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44420</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>44420</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44424</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44426</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44426</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44426</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44428</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44433</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44433</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44438</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44438</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44449</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44449</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44453</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>44455</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44459</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44470</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44470</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>44472</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44473</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44473</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44474</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44476</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44476</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44477</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44477</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44483</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44489</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>44490</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44490</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44496</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44496</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>44496</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44496</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44496</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44497</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44497</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44498</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44498</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44498</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44498</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44498</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>44501</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>44503</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>44503</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>44503</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44505</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44505</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44505</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>44510</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44512</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44516</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44516</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44518</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44519</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44519</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>44519</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44523</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44524</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44525</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44526</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44526</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44526</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44530</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>44531</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44533</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44533</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44551</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>44551</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44585</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44585</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44585</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44586</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44592</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44592</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44594</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44595</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44607</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44615</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44632</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44637</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44642</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44652</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44652</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44662</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44662</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44672</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44674</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44674</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44678</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44681</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44687</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44687</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>44687</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44687</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44687</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44694</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44694</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44694</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44697</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>44698</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44698</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44701</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44708</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44708</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44708</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>44708</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44708</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44708</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>44709</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44711</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44711</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44713</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>44719</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>44722</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>44726</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44726</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44727</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44728</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44728</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>44729</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44740</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>44739</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44741</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44742</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44742</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44744</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44747</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>44747</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>44749</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>44751</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44750</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44750</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44754</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44755</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44755</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44755</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>44755</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44756</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44756</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44757</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44762</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>44761</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>44761</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>44768</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>44770</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44770</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>44774</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>44775</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>44779</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44778</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44779</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44781</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44781</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44783</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44796</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44795</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>44795</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44798</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44799</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44799</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44803</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44803</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44803</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44803</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44803</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44803</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>44806</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44807</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44809</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44809</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44813</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44813</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44813</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44813</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44814</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44816</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44816</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44816</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44816</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44818</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>44818</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44818</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>44818</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44818</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44819</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44820</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44826</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>44826</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44830</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44832</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44834</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44839</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44839</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44846</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44846</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44846</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44847</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44848</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>44847</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>44852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44855</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44858</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44858</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44859</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>44859</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>44860</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44860</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44862</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>44862</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44866</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>44868</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44872</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44872</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44876</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>44879</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>44886</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>44886</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44886</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>44887</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44888</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44888</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44894</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44908</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44908</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>44908</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44908</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>44908</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44908</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>44911</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44911</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>44915</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44917</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44917</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44922</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44925</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>44925</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>44928</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>44929</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44936</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44936</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44936</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44936</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>44936</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>44936</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44936</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44937</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44938</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44938</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>44943</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>44943</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>44943</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44943</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>44950</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44950</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44951</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44952</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>44952</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44952</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44952</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44952</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44952</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44954</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44953</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44958</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44959</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44960</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44960</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44960</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44964</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44966</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44966</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44967</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44967</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44970</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44970</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44970</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44971</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44973</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44973</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44977</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44978</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>44978</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>44977</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>44980</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44984</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44984</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44984</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44985</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44985</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44986</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44986</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44986</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44987</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44988</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>44988</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>44988</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44988</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44988</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44992</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>44993</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>44993</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>44994</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45000</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45005</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45005</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45005</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45009</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45010</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45010</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45010</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45010</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45010</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45010</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45009</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45014</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45014</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>45016</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45030</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>45035</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45036</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45037</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45038</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45040</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45041</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45042</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45042</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45044</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45044</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45048</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45051</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45061</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45068</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45068</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45068</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45068</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45068</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45068</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45072</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45072</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45072</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45077</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45077</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45077</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45077</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>45078</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45078</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45078</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45078</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45078</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45078</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>45078</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45078</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45079</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45078</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45078</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45078</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45079</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45079</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45079</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45084</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45091</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45092</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45092</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45092</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>45092</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45092</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45092</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>45092</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45092</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45093</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45093</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>45093</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45096</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45098</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45098</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45099</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45099</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45099</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45099</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45099</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45099</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45103</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45103</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45103</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45103</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45103</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45103</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45103</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45103</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45103</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45103</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45105</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45107</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45107</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45112</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>45112</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45113</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45114</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45114</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>45114</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45114</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45114</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45113</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45114</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45114</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45114</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45113</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45113</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45113</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45113</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45113</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45114</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45114</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45114</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45114</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45117</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45119</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>45119</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45119</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45119</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45120</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45120</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45120</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>45120</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45121</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45121</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45121</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45126</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45127</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45135</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45135</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45140</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45147</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45147</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45147</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45149</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45149</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45149</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45149</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45152</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45154</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>45154</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45154</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45154</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45156</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45156</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45157</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45156</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46961,7 +46961,7 @@
         <v>45159</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45159</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45160</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45160</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47199,7 +47199,7 @@
         <v>45161</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45162</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45163</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45163</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45166</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45166</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45166</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45167</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45167</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45169</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45173</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45173</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45173</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45173</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45175</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45175</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45175</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45175</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45174</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45175</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45175</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45176</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>45177</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45180</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45180</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45182</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45184</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45187</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45187</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45187</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45188</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45188</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45188</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45189</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49227,7 +49227,7 @@
         <v>45189</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45189</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45190</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45190</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45191</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45194</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45196</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45196</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45198</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45198</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>45199</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45198</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45198</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45201</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45201</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45203</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45204</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45204</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45205</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45206</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45206</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45208</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45210</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45214</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>45215</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45217</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45218</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45218</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45221</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45222</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45223</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>45224</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45224</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45224</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45229</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>45233</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45235</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>45236</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>45236</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>45236</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51751,7 +51751,7 @@
         <v>45239</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>45240</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51875,7 +51875,7 @@
         <v>45240</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51930,14 +51930,14 @@
     <row r="826" ht="15" customHeight="1">
       <c r="A826" t="inlineStr">
         <is>
-          <t>A 56961-2023</t>
+          <t>A 56826-2023</t>
         </is>
       </c>
       <c r="B826" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51951,11 +51951,11 @@
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="G826" t="n">
-        <v>10.8</v>
+        <v>2.5</v>
       </c>
       <c r="H826" t="n">
         <v>0</v>
@@ -51992,14 +51992,14 @@
     <row r="827" ht="15" customHeight="1">
       <c r="A827" t="inlineStr">
         <is>
-          <t>A 57920-2023</t>
+          <t>A 56961-2023</t>
         </is>
       </c>
       <c r="B827" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52011,8 +52011,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="G827" t="n">
-        <v>1.2</v>
+        <v>10.8</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -52049,14 +52054,14 @@
     <row r="828" ht="15" customHeight="1">
       <c r="A828" t="inlineStr">
         <is>
-          <t>A 56826-2023</t>
+          <t>A 57920-2023</t>
         </is>
       </c>
       <c r="B828" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52068,13 +52073,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F828" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="G828" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -52118,7 +52118,7 @@
         <v>45245</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52173,14 +52173,14 @@
     <row r="830" ht="15" customHeight="1">
       <c r="A830" t="inlineStr">
         <is>
-          <t>A 57641-2023</t>
+          <t>A 57788-2023</t>
         </is>
       </c>
       <c r="B830" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52192,8 +52192,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G830" t="n">
-        <v>2.6</v>
+        <v>7.7</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -52230,14 +52235,14 @@
     <row r="831" ht="15" customHeight="1">
       <c r="A831" t="inlineStr">
         <is>
-          <t>A 57632-2023</t>
+          <t>A 57641-2023</t>
         </is>
       </c>
       <c r="B831" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52250,7 +52255,7 @@
         </is>
       </c>
       <c r="G831" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -52287,14 +52292,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 57788-2023</t>
+          <t>A 57632-2023</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52306,13 +52311,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F832" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G832" t="n">
-        <v>7.7</v>
+        <v>2.1</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -52356,7 +52356,7 @@
         <v>45247</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45250</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>45257</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>45257</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y836"/>
+  <dimension ref="A1:Y837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44354</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45114</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>43423</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43402</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>44210</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>43472</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>43664</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>44125</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44026</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>44498</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45177</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>44470</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44854</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44861</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44960</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>43738</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>43738</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>44418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44960</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>45182</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44015</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44139</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44860</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44986</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44987</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>45016</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45191</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45201</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>43427</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>43439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43636</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>43803</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>43888</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>43936</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44082</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44082</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44393</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44393</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44501</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44764</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44817</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44823</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44925</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44985</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45112</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45113</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45113</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45208</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>43339</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>43374</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>43440</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>43445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>43473</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>43493</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>43500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>43500</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>43501</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>43504</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>43504</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>43504</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>43504</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>43507</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>43510</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>43516</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>43517</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>43517</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>43523</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>43531</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>43536</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>43539</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43544</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>43559</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>43585</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>43585</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43585</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>43585</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>43587</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43591</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43601</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>43614</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>43636</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43664</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>43664</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>43664</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43686</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43697</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43700</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43705</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>43707</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>43709</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43738</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43738</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43738</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43739</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>43740</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43748</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>43752</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>43753</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43754</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>43755</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>43760</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>43761</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>43768</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>43768</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>43769</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>43769</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43787</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43787</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43794</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43794</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43795</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43803</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43803</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43803</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>43805</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>43810</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43818</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43833</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43841</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>43843</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>43843</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>43845</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>43852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>43859</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>43888</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>43924</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>43936</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>43936</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>43961</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>43976</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>43980</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43980</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43983</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43987</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43993</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43993</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43993</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44004</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44007</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44014</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44026</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44028</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44029</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44029</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44029</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>44029</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44029</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44050</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>44054</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>44060</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44071</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44078</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44082</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44082</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>44089</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44089</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44089</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44089</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44090</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44090</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44090</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44090</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44096</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44106</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44106</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44106</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44115</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44116</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44117</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44125</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44132</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44132</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44132</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44133</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44134</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44141</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44147</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44147</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44148</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44151</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44151</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44151</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>44152</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>44161</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44163</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44166</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44168</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44170</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44170</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44175</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44186</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44193</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44207</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44210</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44211</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44218</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44218</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44230</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44231</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44231</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44231</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44323</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44328</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44341</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44344</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44344</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44344</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44350</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44350</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>44351</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44356</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44357</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44357</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>44368</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44371</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>44377</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44377</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44377</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>44377</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44377</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44377</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44377</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>44378</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44379</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44379</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44381</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>44382</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44386</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44386</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44386</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>44386</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44391</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44390</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>44391</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44390</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44392</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44393</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44393</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>44399</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>44404</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44407</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44417</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>44418</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44420</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44420</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>44420</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44424</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44426</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44426</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44426</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44428</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44433</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44433</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44438</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44438</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44449</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44449</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44453</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>44455</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44459</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44470</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44470</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>44472</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44473</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44473</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44474</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44476</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44476</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44477</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44477</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44483</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44489</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>44490</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44490</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44496</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44496</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>44496</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44496</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44496</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44497</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44497</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44498</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44498</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44498</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44498</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44498</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>44501</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>44503</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>44503</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>44503</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44505</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44505</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44505</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>44510</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44512</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44516</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44516</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44518</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44519</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44519</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>44519</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44523</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44524</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44525</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44526</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44526</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44526</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44530</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>44531</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44533</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44533</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44551</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>44551</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44585</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44585</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44585</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44586</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44592</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44592</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44594</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44595</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44607</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44615</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44632</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44637</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44642</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44652</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44652</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44662</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44662</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44672</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44674</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44674</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44678</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44681</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44687</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44687</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>44687</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44687</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44687</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44694</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44694</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44694</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44697</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>44698</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44698</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44701</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44708</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44708</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44708</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>44708</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44708</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44708</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>44709</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44711</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44711</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44713</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>44719</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>44722</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>44726</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44726</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44727</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44728</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44728</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>44729</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44740</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>44739</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44741</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44742</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44742</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44744</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44747</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>44747</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>44749</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>44751</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44750</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44750</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44754</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44755</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44755</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44755</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>44755</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44756</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44756</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44757</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44762</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>44761</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>44761</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>44768</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>44770</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44770</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>44774</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>44775</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>44779</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44778</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44779</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44781</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44781</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44783</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44796</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44795</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>44795</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44798</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44799</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44799</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44803</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44803</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44803</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44803</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44803</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44803</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>44806</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44807</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44809</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44809</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44813</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44813</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44813</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44813</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44814</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44816</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44816</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44816</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44816</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44818</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>44818</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44818</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>44818</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44818</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44819</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44820</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44826</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>44826</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44830</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44832</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44834</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44839</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44839</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44846</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44846</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44846</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44847</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44848</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>44847</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>44852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44855</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44858</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44858</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44859</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>44859</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>44860</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44860</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44862</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>44862</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44866</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>44868</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44872</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44872</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44876</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>44879</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>44886</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>44886</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44886</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>44887</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44888</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44888</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44894</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44908</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44908</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>44908</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44908</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>44908</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44908</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>44911</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44911</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>44915</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44917</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44917</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44922</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44925</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>44925</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>44928</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>44929</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44936</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44936</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44936</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44936</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>44936</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>44936</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44936</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44937</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44938</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44938</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>44943</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>44943</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>44943</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44943</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>44950</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44950</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44951</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44952</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>44952</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44952</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44952</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44952</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44952</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44954</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44953</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44958</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44959</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44960</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44960</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44960</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44964</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44966</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44966</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44967</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44967</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44970</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44970</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44970</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44971</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44973</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44973</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44977</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44978</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>44978</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>44977</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>44980</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44984</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44984</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44984</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44985</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44985</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44986</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44986</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44986</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44987</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44988</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>44988</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>44988</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44988</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44988</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44992</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>44993</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>44993</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>44994</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45000</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45005</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45005</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45005</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45009</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45010</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45010</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45010</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45010</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45010</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45010</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45009</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45014</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45014</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>45016</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45030</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>45035</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45036</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45037</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45038</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45040</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45041</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45042</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45042</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45044</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45044</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45048</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45051</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45061</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45068</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45068</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45068</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45068</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45068</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45068</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45072</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45072</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45072</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45077</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45077</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45077</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45077</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>45078</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45078</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45078</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45078</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45078</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45078</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>45078</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45078</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45079</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45078</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45078</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45078</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45079</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45079</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45079</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45084</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45091</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45092</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45092</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45092</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>45092</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45092</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45092</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>45092</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45092</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45093</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45093</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>45093</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45096</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45098</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45098</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45099</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45099</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45099</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45099</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45099</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45099</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45103</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45103</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45103</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45103</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45103</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45103</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45103</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45103</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45103</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45103</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45105</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45107</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45107</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45112</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>45112</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45113</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45114</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45114</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>45114</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45114</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45114</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45113</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45114</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45114</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45114</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45113</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45113</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45113</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45113</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45113</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45114</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45114</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45114</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45114</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45117</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45119</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>45119</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45119</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45119</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45120</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45120</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45120</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>45120</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45121</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45121</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45121</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45126</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45127</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45135</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45135</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45140</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45147</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45147</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45147</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45149</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45149</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45149</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45149</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45152</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45154</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>45154</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45154</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45154</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45156</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45156</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45157</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45156</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46961,7 +46961,7 @@
         <v>45159</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45159</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45160</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45160</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47199,7 +47199,7 @@
         <v>45161</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45162</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45163</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45163</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45166</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45166</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45166</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45167</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45167</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45169</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45173</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45173</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45173</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45173</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45175</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45175</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45175</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45175</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45174</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45175</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45175</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45176</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>45177</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45180</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45180</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45182</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45184</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45187</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45187</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45187</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45188</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45188</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45188</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45189</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49227,7 +49227,7 @@
         <v>45189</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45189</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45190</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45190</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45191</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45194</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45196</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45196</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45198</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45198</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>45199</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45198</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45198</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45201</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45201</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45203</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45204</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45204</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45205</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45206</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45206</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45208</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45210</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45214</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>45215</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45217</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45218</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45218</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45221</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45222</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45223</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>45224</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45224</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45224</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45229</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>45233</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45235</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>45236</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>45236</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>45236</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51744,14 +51744,14 @@
     <row r="823" ht="15" customHeight="1">
       <c r="A823" t="inlineStr">
         <is>
-          <t>A 56981-2023</t>
+          <t>A 55920-2023</t>
         </is>
       </c>
       <c r="B823" s="1" t="n">
-        <v>45239</v>
+        <v>45240</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51765,11 +51765,11 @@
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="G823" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -51806,14 +51806,14 @@
     <row r="824" ht="15" customHeight="1">
       <c r="A824" t="inlineStr">
         <is>
-          <t>A 55920-2023</t>
+          <t>A 56981-2023</t>
         </is>
       </c>
       <c r="B824" s="1" t="n">
-        <v>45240</v>
+        <v>45239</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51827,11 +51827,11 @@
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="G824" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -51875,7 +51875,7 @@
         <v>45240</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51937,7 +51937,7 @@
         <v>45244</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51992,14 +51992,14 @@
     <row r="827" ht="15" customHeight="1">
       <c r="A827" t="inlineStr">
         <is>
-          <t>A 56961-2023</t>
+          <t>A 57920-2023</t>
         </is>
       </c>
       <c r="B827" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52011,13 +52011,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F827" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="G827" t="n">
-        <v>10.8</v>
+        <v>1.2</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -52054,14 +52049,14 @@
     <row r="828" ht="15" customHeight="1">
       <c r="A828" t="inlineStr">
         <is>
-          <t>A 57920-2023</t>
+          <t>A 56961-2023</t>
         </is>
       </c>
       <c r="B828" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52073,8 +52068,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="G828" t="n">
-        <v>1.2</v>
+        <v>10.8</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -52118,7 +52118,7 @@
         <v>45245</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52173,14 +52173,14 @@
     <row r="830" ht="15" customHeight="1">
       <c r="A830" t="inlineStr">
         <is>
-          <t>A 57788-2023</t>
+          <t>A 57632-2023</t>
         </is>
       </c>
       <c r="B830" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52192,13 +52192,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F830" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G830" t="n">
-        <v>7.7</v>
+        <v>2.1</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -52242,7 +52237,7 @@
         <v>45246</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52292,14 +52287,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 57632-2023</t>
+          <t>A 57788-2023</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52311,8 +52306,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G832" t="n">
-        <v>2.1</v>
+        <v>7.7</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -52356,7 +52356,7 @@
         <v>45247</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45250</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>45257</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52532,7 +52532,7 @@
       </c>
       <c r="R835" s="2" t="inlineStr"/>
     </row>
-    <row r="836">
+    <row r="836" ht="15" customHeight="1">
       <c r="A836" t="inlineStr">
         <is>
           <t>A 60348-2023</t>
@@ -52542,7 +52542,7 @@
         <v>45257</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52588,6 +52588,63 @@
         <v>0</v>
       </c>
       <c r="R836" s="2" t="inlineStr"/>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>A 61200-2023</t>
+        </is>
+      </c>
+      <c r="B837" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="C837" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>ÅSELE</t>
+        </is>
+      </c>
+      <c r="G837" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H837" t="n">
+        <v>0</v>
+      </c>
+      <c r="I837" t="n">
+        <v>0</v>
+      </c>
+      <c r="J837" t="n">
+        <v>0</v>
+      </c>
+      <c r="K837" t="n">
+        <v>0</v>
+      </c>
+      <c r="L837" t="n">
+        <v>0</v>
+      </c>
+      <c r="M837" t="n">
+        <v>0</v>
+      </c>
+      <c r="N837" t="n">
+        <v>0</v>
+      </c>
+      <c r="O837" t="n">
+        <v>0</v>
+      </c>
+      <c r="P837" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q837" t="n">
+        <v>0</v>
+      </c>
+      <c r="R837" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y837"/>
+  <dimension ref="A1:Y840"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44354</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45114</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>43423</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43402</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>44210</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>43472</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>43664</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>44125</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44026</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>44498</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45177</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>44470</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44854</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44861</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44960</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>43738</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>43738</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>44418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44960</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>45182</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44015</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44139</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44860</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44986</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44987</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>45016</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45191</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45201</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>43427</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>43439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43636</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>43803</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>43888</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>43936</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44082</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44082</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44393</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44393</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44501</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44764</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44817</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44823</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44925</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44985</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45112</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45113</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45113</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45208</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>43339</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>43374</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>43440</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>43445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>43473</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>43493</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>43500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>43500</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>43501</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>43504</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>43504</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>43504</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>43504</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>43507</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>43510</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>43516</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>43517</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>43517</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>43523</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>43531</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>43536</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>43539</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43544</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>43559</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>43585</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>43585</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43585</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>43585</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>43587</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43591</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43601</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>43614</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>43636</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43664</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>43664</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>43664</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43686</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43697</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43700</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43705</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>43707</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>43709</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43738</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43738</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43738</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43739</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>43740</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43748</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>43752</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>43753</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43754</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>43755</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>43760</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>43761</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>43768</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>43768</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>43769</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>43769</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43787</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43787</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43794</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43794</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43795</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43803</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43803</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43803</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>43805</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>43810</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43818</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43833</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43841</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>43843</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>43843</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>43845</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>43852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>43859</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>43888</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>43924</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>43936</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>43936</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>43961</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>43976</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>43980</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43980</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43983</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43987</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43993</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43993</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43993</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44004</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44007</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44014</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44026</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44028</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44029</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44029</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44029</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>44029</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44029</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44050</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>44054</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>44060</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44071</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44078</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44082</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44082</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>44089</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44089</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44089</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44089</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44090</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44090</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44090</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44090</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44096</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44106</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44106</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44106</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44115</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44116</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44117</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44125</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44132</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44132</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44132</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44133</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44134</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44141</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44147</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44147</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44148</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44151</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44151</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44151</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>44152</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>44161</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44163</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44166</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44168</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44170</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44170</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44175</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44186</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44193</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44207</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44210</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44211</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44218</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44218</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44230</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44231</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44231</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44231</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44323</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44328</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44341</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44344</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44344</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44344</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44350</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44350</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>44351</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44356</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44357</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44357</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>44368</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44371</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>44377</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44377</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44377</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>44377</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44377</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44377</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44377</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>44378</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44379</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44379</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44381</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>44382</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44386</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44386</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44386</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>44386</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44391</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44390</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>44391</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44390</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44392</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44393</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44393</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>44399</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>44404</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44407</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44417</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>44418</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44420</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44420</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>44420</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44424</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44426</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44426</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44426</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44428</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44433</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44433</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44438</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44438</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44449</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44449</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44453</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>44455</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44459</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44470</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44470</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>44472</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44473</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44473</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44474</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44476</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44476</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44477</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44477</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44483</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44489</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>44490</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44490</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44496</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44496</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>44496</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44496</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44496</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44497</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44497</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44498</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44498</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44498</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44498</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44498</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>44501</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>44503</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>44503</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>44503</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44505</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44505</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44505</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>44510</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44512</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44516</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44516</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44518</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44519</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44519</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>44519</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44523</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44524</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44525</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44526</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44526</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44526</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44530</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>44531</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44533</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44533</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44551</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>44551</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44585</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44585</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44585</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44586</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44592</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44592</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44594</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44595</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44607</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44615</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44632</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44637</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44642</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44652</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44652</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44662</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44662</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44672</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44674</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44674</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44678</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44681</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44687</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44687</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>44687</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44687</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44687</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44694</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44694</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44694</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44697</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>44698</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44698</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44701</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44708</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44708</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44708</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>44708</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44708</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44708</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>44709</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44711</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44711</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44713</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>44719</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>44722</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>44726</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44726</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44727</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44728</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44728</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>44729</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44740</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>44739</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44741</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44742</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44742</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44744</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44747</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>44747</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>44749</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>44751</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44750</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44750</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44754</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44755</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44755</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44755</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>44755</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44756</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44756</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44757</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44762</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>44761</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>44761</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>44768</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>44770</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44770</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>44774</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>44775</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>44779</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44778</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44779</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44781</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44781</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44783</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44796</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44795</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>44795</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44798</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44799</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44799</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44803</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44803</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44803</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44803</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44803</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44803</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>44806</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44807</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44809</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44809</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44813</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44813</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44813</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44813</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44814</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44816</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44816</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44816</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44816</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44818</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>44818</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44818</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>44818</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44818</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44819</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44820</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44826</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>44826</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44830</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44832</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44834</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44839</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44839</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44846</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44846</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44846</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44847</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44848</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>44847</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>44852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44855</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44858</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44858</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44859</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>44859</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>44860</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44860</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44862</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>44862</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44866</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>44868</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44872</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44872</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44876</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>44879</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>44886</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>44886</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44886</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>44887</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44888</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44888</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44894</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44908</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44908</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>44908</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44908</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>44908</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44908</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>44911</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44911</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>44915</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44917</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44917</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44922</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44925</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>44925</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>44928</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>44929</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44936</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44936</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44936</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44936</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>44936</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>44936</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44936</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44937</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44938</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44938</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>44943</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>44943</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>44943</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44943</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>44950</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44950</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44951</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44952</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>44952</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44952</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44952</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44952</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44952</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44954</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44953</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44958</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44959</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44960</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44960</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44960</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44964</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44966</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44966</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44967</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44967</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44970</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44970</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44970</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44971</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44973</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44973</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44977</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44978</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>44978</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>44977</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>44980</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44984</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44984</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44984</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44985</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44985</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44986</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44986</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44986</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44987</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44988</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>44988</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>44988</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44988</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44988</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44992</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>44993</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>44993</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>44994</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45000</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45005</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45005</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45005</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45009</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45010</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45010</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45010</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45010</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45010</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45010</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45009</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45014</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45014</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>45016</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45030</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>45035</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45036</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45037</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45038</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45040</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45041</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45042</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45042</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45044</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45044</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45048</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45051</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45061</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45068</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45068</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45068</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45068</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45068</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45068</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45072</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45072</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45072</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45077</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45077</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45077</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45077</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>45078</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45078</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45078</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45078</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45078</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45078</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>45078</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45078</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45079</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45078</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45078</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45078</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45079</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45079</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45079</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45084</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45091</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45092</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45092</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45092</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>45092</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45092</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45092</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>45092</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45092</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45093</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45093</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>45093</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45096</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45098</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45098</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45099</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45099</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45099</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45099</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45099</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45099</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45103</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45103</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45103</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45103</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45103</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45103</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45103</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45103</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45103</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45103</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45105</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45107</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45107</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45112</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>45112</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45113</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45114</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45114</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>45114</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45114</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45114</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45113</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45114</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45114</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45114</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45113</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45113</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45113</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45113</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45113</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45114</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45114</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45114</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45114</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45117</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45119</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>45119</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45119</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45119</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45120</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45120</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45120</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>45120</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45121</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45121</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45121</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45126</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45127</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45135</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45135</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45140</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45147</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45147</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45147</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45149</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45149</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45149</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45149</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45152</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45154</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>45154</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45154</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45154</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45156</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45156</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45157</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45156</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46961,7 +46961,7 @@
         <v>45159</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45159</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45160</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45160</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47199,7 +47199,7 @@
         <v>45161</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45162</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45163</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45163</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45166</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45166</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45166</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45167</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45167</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45169</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45173</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45173</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45173</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45173</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45175</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45175</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45175</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45175</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45174</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45175</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45175</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45176</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>45177</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45180</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45180</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45182</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45184</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45187</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45187</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45187</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45188</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45188</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45188</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45189</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49227,7 +49227,7 @@
         <v>45189</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45189</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45190</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45190</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45191</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45194</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45196</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45196</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45198</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45198</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>45199</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45198</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45198</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45201</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45201</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45203</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45204</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45204</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45205</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45206</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45206</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45208</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45210</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45214</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>45215</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45217</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45218</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45218</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45221</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45222</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45223</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>45224</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45224</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45224</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45229</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>45233</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45235</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>45236</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>45236</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>45236</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51744,14 +51744,14 @@
     <row r="823" ht="15" customHeight="1">
       <c r="A823" t="inlineStr">
         <is>
-          <t>A 55920-2023</t>
+          <t>A 56981-2023</t>
         </is>
       </c>
       <c r="B823" s="1" t="n">
-        <v>45240</v>
+        <v>45239</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51765,11 +51765,11 @@
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="G823" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -51806,14 +51806,14 @@
     <row r="824" ht="15" customHeight="1">
       <c r="A824" t="inlineStr">
         <is>
-          <t>A 56981-2023</t>
+          <t>A 55920-2023</t>
         </is>
       </c>
       <c r="B824" s="1" t="n">
-        <v>45239</v>
+        <v>45240</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51827,11 +51827,11 @@
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="G824" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -51875,7 +51875,7 @@
         <v>45240</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51937,7 +51937,7 @@
         <v>45244</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51992,14 +51992,14 @@
     <row r="827" ht="15" customHeight="1">
       <c r="A827" t="inlineStr">
         <is>
-          <t>A 57920-2023</t>
+          <t>A 56961-2023</t>
         </is>
       </c>
       <c r="B827" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52011,8 +52011,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="G827" t="n">
-        <v>1.2</v>
+        <v>10.8</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -52049,14 +52054,14 @@
     <row r="828" ht="15" customHeight="1">
       <c r="A828" t="inlineStr">
         <is>
-          <t>A 56961-2023</t>
+          <t>A 57920-2023</t>
         </is>
       </c>
       <c r="B828" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52068,13 +52073,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F828" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="G828" t="n">
-        <v>10.8</v>
+        <v>1.2</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -52118,7 +52118,7 @@
         <v>45245</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52173,14 +52173,14 @@
     <row r="830" ht="15" customHeight="1">
       <c r="A830" t="inlineStr">
         <is>
-          <t>A 57632-2023</t>
+          <t>A 57641-2023</t>
         </is>
       </c>
       <c r="B830" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
         </is>
       </c>
       <c r="G830" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -52230,14 +52230,14 @@
     <row r="831" ht="15" customHeight="1">
       <c r="A831" t="inlineStr">
         <is>
-          <t>A 57641-2023</t>
+          <t>A 57788-2023</t>
         </is>
       </c>
       <c r="B831" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52249,8 +52249,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G831" t="n">
-        <v>2.6</v>
+        <v>7.7</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -52287,14 +52292,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 57788-2023</t>
+          <t>A 57632-2023</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52306,13 +52311,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F832" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G832" t="n">
-        <v>7.7</v>
+        <v>2.1</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -52356,7 +52356,7 @@
         <v>45247</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45250</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>45257</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>45257</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
       </c>
       <c r="R836" s="2" t="inlineStr"/>
     </row>
-    <row r="837">
+    <row r="837" ht="15" customHeight="1">
       <c r="A837" t="inlineStr">
         <is>
           <t>A 61200-2023</t>
@@ -52599,7 +52599,7 @@
         <v>45260</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52645,6 +52645,187 @@
         <v>0</v>
       </c>
       <c r="R837" s="2" t="inlineStr"/>
+    </row>
+    <row r="838" ht="15" customHeight="1">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>A 61568-2023</t>
+        </is>
+      </c>
+      <c r="B838" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C838" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>ÅSELE</t>
+        </is>
+      </c>
+      <c r="G838" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H838" t="n">
+        <v>0</v>
+      </c>
+      <c r="I838" t="n">
+        <v>0</v>
+      </c>
+      <c r="J838" t="n">
+        <v>0</v>
+      </c>
+      <c r="K838" t="n">
+        <v>0</v>
+      </c>
+      <c r="L838" t="n">
+        <v>0</v>
+      </c>
+      <c r="M838" t="n">
+        <v>0</v>
+      </c>
+      <c r="N838" t="n">
+        <v>0</v>
+      </c>
+      <c r="O838" t="n">
+        <v>0</v>
+      </c>
+      <c r="P838" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q838" t="n">
+        <v>0</v>
+      </c>
+      <c r="R838" s="2" t="inlineStr"/>
+    </row>
+    <row r="839" ht="15" customHeight="1">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>A 61800-2023</t>
+        </is>
+      </c>
+      <c r="B839" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="C839" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>ÅSELE</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="G839" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H839" t="n">
+        <v>0</v>
+      </c>
+      <c r="I839" t="n">
+        <v>0</v>
+      </c>
+      <c r="J839" t="n">
+        <v>0</v>
+      </c>
+      <c r="K839" t="n">
+        <v>0</v>
+      </c>
+      <c r="L839" t="n">
+        <v>0</v>
+      </c>
+      <c r="M839" t="n">
+        <v>0</v>
+      </c>
+      <c r="N839" t="n">
+        <v>0</v>
+      </c>
+      <c r="O839" t="n">
+        <v>0</v>
+      </c>
+      <c r="P839" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q839" t="n">
+        <v>0</v>
+      </c>
+      <c r="R839" s="2" t="inlineStr"/>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>A 61801-2023</t>
+        </is>
+      </c>
+      <c r="B840" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="C840" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>ÅSELE</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="G840" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H840" t="n">
+        <v>0</v>
+      </c>
+      <c r="I840" t="n">
+        <v>0</v>
+      </c>
+      <c r="J840" t="n">
+        <v>0</v>
+      </c>
+      <c r="K840" t="n">
+        <v>0</v>
+      </c>
+      <c r="L840" t="n">
+        <v>0</v>
+      </c>
+      <c r="M840" t="n">
+        <v>0</v>
+      </c>
+      <c r="N840" t="n">
+        <v>0</v>
+      </c>
+      <c r="O840" t="n">
+        <v>0</v>
+      </c>
+      <c r="P840" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q840" t="n">
+        <v>0</v>
+      </c>
+      <c r="R840" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y840"/>
+  <dimension ref="A1:Y845"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44354</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45114</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>43423</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43402</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>44210</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>43472</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>43664</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>44125</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44026</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>44498</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45177</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>44470</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44854</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44861</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44960</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>43738</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>43738</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>44418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44960</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>45182</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44015</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44139</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44860</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44986</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44987</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>45016</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45191</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45201</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>43427</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>43439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43636</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>43803</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>43888</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>43936</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44082</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44082</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44393</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44393</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44501</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44764</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44817</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44823</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44925</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44985</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45112</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45113</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45113</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45208</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>43339</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>43374</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>43440</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>43445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>43473</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>43493</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>43500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>43500</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>43501</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>43504</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>43504</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>43504</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>43504</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>43507</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>43510</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>43516</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>43517</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>43517</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>43523</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>43531</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>43536</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>43539</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43544</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>43559</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>43585</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>43585</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43585</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>43585</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>43587</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43591</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43601</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>43614</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>43636</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43664</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>43664</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>43664</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43686</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43697</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43700</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43705</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>43707</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>43709</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43738</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43738</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43738</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43739</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>43740</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43748</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>43752</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>43753</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43754</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>43755</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>43760</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>43761</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>43768</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>43768</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>43769</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>43769</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43787</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43787</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43794</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43794</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43795</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43803</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43803</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43803</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>43805</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>43810</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43818</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43833</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43841</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>43843</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>43843</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>43845</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>43852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>43859</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>43888</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>43924</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>43936</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>43936</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>43961</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>43976</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>43980</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43980</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43983</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43987</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43993</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43993</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43993</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44004</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44007</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44014</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44026</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44028</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44029</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44029</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44029</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>44029</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44029</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44050</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>44054</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>44060</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44071</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44078</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44082</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44082</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>44089</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44089</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44089</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44089</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44090</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44090</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44090</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44090</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44096</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44106</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44106</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44106</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44115</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44116</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44117</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44125</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44132</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44132</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44132</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44133</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44134</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44141</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44147</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44147</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44148</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44151</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44151</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44151</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>44152</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>44161</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44163</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44166</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44168</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44170</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44170</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44175</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44186</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44193</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44207</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44210</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44211</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44218</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44218</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44230</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44231</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44231</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44231</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44323</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44328</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44341</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44344</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44344</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44344</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44350</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44350</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>44351</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44356</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44357</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44357</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>44368</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44371</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>44377</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44377</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44377</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>44377</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44377</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44377</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44377</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>44378</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44379</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44379</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44381</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>44382</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44386</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44386</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44386</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>44386</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44391</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44390</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>44391</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44390</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44392</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44393</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44393</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>44399</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>44404</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44407</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44417</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>44418</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44420</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44420</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>44420</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44424</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44426</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44426</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44426</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44428</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44433</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44433</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44438</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44438</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44449</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44449</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44453</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>44455</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44459</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44470</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44470</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>44472</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44473</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44473</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44474</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44476</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44476</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44477</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44477</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44483</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44489</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>44490</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44490</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44496</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44496</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>44496</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44496</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44496</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44497</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44497</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44498</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44498</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44498</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44498</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44498</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>44501</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>44503</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>44503</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>44503</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44505</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44505</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44505</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>44510</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44512</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44516</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44516</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44518</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44519</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44519</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>44519</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44523</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44524</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44525</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44526</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44526</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44526</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44530</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>44531</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44533</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44533</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44551</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>44551</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44585</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44585</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44585</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44586</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44592</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44592</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44594</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44595</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44607</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44615</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44632</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44637</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44642</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44652</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44652</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44662</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44662</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44672</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44674</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44674</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44678</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44681</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44687</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44687</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>44687</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44687</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44687</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44694</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44694</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44694</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44697</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>44698</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44698</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44701</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44708</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44708</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44708</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>44708</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44708</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44708</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>44709</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44711</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44711</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44713</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>44719</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>44722</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>44726</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44726</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44727</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44728</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44728</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>44729</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44740</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>44739</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44741</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44742</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44742</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44744</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44747</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>44747</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>44749</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>44751</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44750</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44750</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44754</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44755</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44755</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44755</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>44755</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44756</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44756</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44757</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44762</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>44761</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>44761</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>44768</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>44770</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44770</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>44774</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>44775</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>44779</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44778</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44779</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44781</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44781</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44783</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44796</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44795</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>44795</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44798</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44799</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44799</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44803</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44803</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44803</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44803</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44803</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44803</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>44806</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44807</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44809</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44809</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44813</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44813</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44813</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44813</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44814</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44816</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44816</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44816</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44816</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44818</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>44818</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44818</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>44818</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44818</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44819</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44820</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44826</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>44826</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44830</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44832</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44834</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44839</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44839</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44846</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44846</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44846</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44847</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44848</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>44847</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>44852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44855</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44858</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44858</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44859</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>44859</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>44860</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44860</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44862</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>44862</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44866</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>44868</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44872</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44872</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44876</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>44879</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>44886</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>44886</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44886</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>44887</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44888</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44888</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44894</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44908</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44908</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>44908</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44908</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>44908</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44908</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>44911</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44911</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>44915</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44917</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44917</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44922</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44925</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>44925</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>44928</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>44929</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44936</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44936</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44936</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44936</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>44936</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>44936</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44936</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44937</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44938</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44938</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>44943</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>44943</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>44943</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44943</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>44950</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44950</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44951</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44952</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>44952</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44952</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44952</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44952</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44952</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44954</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44953</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44958</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44959</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44960</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44960</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44960</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44964</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44966</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44966</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44967</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44967</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44970</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44970</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44970</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44971</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44973</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44973</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44977</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44978</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>44978</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>44977</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>44980</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44984</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44984</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44984</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44985</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44985</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44986</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44986</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44986</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44987</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44988</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>44988</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>44988</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44988</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44988</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44992</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>44993</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>44993</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>44994</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45000</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45005</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45005</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45005</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45009</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45010</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45010</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45010</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45010</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45010</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45010</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45009</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45014</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45014</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>45016</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45030</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>45035</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45036</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45037</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45038</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45040</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45041</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45042</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45042</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45044</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45044</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45048</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45051</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45061</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45068</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45068</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45068</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45068</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45068</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45068</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45072</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45072</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45072</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45077</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45077</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45077</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45077</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>45078</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45078</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45078</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45078</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45078</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45078</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>45078</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45078</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45079</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45078</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45078</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45078</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45079</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45079</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45079</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45084</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45091</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45092</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45092</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45092</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>45092</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45092</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45092</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>45092</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45092</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45093</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45093</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>45093</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45096</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45098</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45098</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45099</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45099</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45099</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45099</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45099</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45099</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45103</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45103</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45103</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45103</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45103</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45103</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45103</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45103</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45103</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45103</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45105</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45107</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45107</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45112</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>45112</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45113</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45114</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45114</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>45114</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45114</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45114</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45113</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45114</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45114</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45114</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45113</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45113</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45113</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45113</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45113</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45114</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45114</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45114</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45114</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45117</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45119</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>45119</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45119</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45119</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45120</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45120</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45120</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>45120</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45121</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45121</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45121</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45126</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45127</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45135</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45135</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45140</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45147</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45147</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45147</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45149</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45149</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45149</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45149</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45152</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45154</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>45154</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45154</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45154</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45156</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45156</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45157</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45156</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46961,7 +46961,7 @@
         <v>45159</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45159</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45160</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45160</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47199,7 +47199,7 @@
         <v>45161</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45162</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45163</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45163</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45166</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45166</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45166</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45167</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45167</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45169</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45173</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45173</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45173</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45173</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45175</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45175</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45175</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45175</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45174</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45175</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45175</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45176</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>45177</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45180</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45180</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45182</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45184</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45187</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45187</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45187</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45188</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45188</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45188</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45189</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49227,7 +49227,7 @@
         <v>45189</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45189</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45190</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45190</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45191</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45194</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45196</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45196</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45198</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45198</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>45199</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45198</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45198</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45201</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45201</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45203</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45204</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45204</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45205</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45206</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45206</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45208</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45210</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45214</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>45215</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45217</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45218</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45218</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45221</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45222</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45223</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>45224</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45224</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45224</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45229</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>45233</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45235</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>45236</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>45236</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>45236</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51744,14 +51744,14 @@
     <row r="823" ht="15" customHeight="1">
       <c r="A823" t="inlineStr">
         <is>
-          <t>A 56981-2023</t>
+          <t>A 55920-2023</t>
         </is>
       </c>
       <c r="B823" s="1" t="n">
-        <v>45239</v>
+        <v>45240</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51765,11 +51765,11 @@
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="G823" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -51806,14 +51806,14 @@
     <row r="824" ht="15" customHeight="1">
       <c r="A824" t="inlineStr">
         <is>
-          <t>A 55920-2023</t>
+          <t>A 56981-2023</t>
         </is>
       </c>
       <c r="B824" s="1" t="n">
-        <v>45240</v>
+        <v>45239</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51827,11 +51827,11 @@
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="G824" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -51875,7 +51875,7 @@
         <v>45240</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51937,7 +51937,7 @@
         <v>45244</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51999,7 +51999,7 @@
         <v>45244</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52061,7 +52061,7 @@
         <v>45244</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>45245</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>45246</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52237,7 +52237,7 @@
         <v>45246</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52299,7 +52299,7 @@
         <v>45246</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52356,7 +52356,7 @@
         <v>45247</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45250</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>45257</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>45257</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52599,7 +52599,7 @@
         <v>45260</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52656,7 +52656,7 @@
         <v>45261</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52713,7 +52713,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
       </c>
       <c r="R839" s="2" t="inlineStr"/>
     </row>
-    <row r="840">
+    <row r="840" ht="15" customHeight="1">
       <c r="A840" t="inlineStr">
         <is>
           <t>A 61801-2023</t>
@@ -52775,7 +52775,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52826,6 +52826,316 @@
         <v>0</v>
       </c>
       <c r="R840" s="2" t="inlineStr"/>
+    </row>
+    <row r="841" ht="15" customHeight="1">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>A 61876-2023</t>
+        </is>
+      </c>
+      <c r="B841" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="C841" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>ÅSELE</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="G841" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H841" t="n">
+        <v>0</v>
+      </c>
+      <c r="I841" t="n">
+        <v>0</v>
+      </c>
+      <c r="J841" t="n">
+        <v>0</v>
+      </c>
+      <c r="K841" t="n">
+        <v>0</v>
+      </c>
+      <c r="L841" t="n">
+        <v>0</v>
+      </c>
+      <c r="M841" t="n">
+        <v>0</v>
+      </c>
+      <c r="N841" t="n">
+        <v>0</v>
+      </c>
+      <c r="O841" t="n">
+        <v>0</v>
+      </c>
+      <c r="P841" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q841" t="n">
+        <v>0</v>
+      </c>
+      <c r="R841" s="2" t="inlineStr"/>
+    </row>
+    <row r="842" ht="15" customHeight="1">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>A 61874-2023</t>
+        </is>
+      </c>
+      <c r="B842" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="C842" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>ÅSELE</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="G842" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H842" t="n">
+        <v>0</v>
+      </c>
+      <c r="I842" t="n">
+        <v>0</v>
+      </c>
+      <c r="J842" t="n">
+        <v>0</v>
+      </c>
+      <c r="K842" t="n">
+        <v>0</v>
+      </c>
+      <c r="L842" t="n">
+        <v>0</v>
+      </c>
+      <c r="M842" t="n">
+        <v>0</v>
+      </c>
+      <c r="N842" t="n">
+        <v>0</v>
+      </c>
+      <c r="O842" t="n">
+        <v>0</v>
+      </c>
+      <c r="P842" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q842" t="n">
+        <v>0</v>
+      </c>
+      <c r="R842" s="2" t="inlineStr"/>
+    </row>
+    <row r="843" ht="15" customHeight="1">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>A 61985-2023</t>
+        </is>
+      </c>
+      <c r="B843" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="C843" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>ÅSELE</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="G843" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H843" t="n">
+        <v>0</v>
+      </c>
+      <c r="I843" t="n">
+        <v>0</v>
+      </c>
+      <c r="J843" t="n">
+        <v>0</v>
+      </c>
+      <c r="K843" t="n">
+        <v>0</v>
+      </c>
+      <c r="L843" t="n">
+        <v>0</v>
+      </c>
+      <c r="M843" t="n">
+        <v>0</v>
+      </c>
+      <c r="N843" t="n">
+        <v>0</v>
+      </c>
+      <c r="O843" t="n">
+        <v>0</v>
+      </c>
+      <c r="P843" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q843" t="n">
+        <v>0</v>
+      </c>
+      <c r="R843" s="2" t="inlineStr"/>
+    </row>
+    <row r="844" ht="15" customHeight="1">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>A 62108-2023</t>
+        </is>
+      </c>
+      <c r="B844" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="C844" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>ÅSELE</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="G844" t="n">
+        <v>4</v>
+      </c>
+      <c r="H844" t="n">
+        <v>0</v>
+      </c>
+      <c r="I844" t="n">
+        <v>0</v>
+      </c>
+      <c r="J844" t="n">
+        <v>0</v>
+      </c>
+      <c r="K844" t="n">
+        <v>0</v>
+      </c>
+      <c r="L844" t="n">
+        <v>0</v>
+      </c>
+      <c r="M844" t="n">
+        <v>0</v>
+      </c>
+      <c r="N844" t="n">
+        <v>0</v>
+      </c>
+      <c r="O844" t="n">
+        <v>0</v>
+      </c>
+      <c r="P844" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q844" t="n">
+        <v>0</v>
+      </c>
+      <c r="R844" s="2" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>A 62109-2023</t>
+        </is>
+      </c>
+      <c r="B845" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="C845" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>ÅSELE</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="G845" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H845" t="n">
+        <v>0</v>
+      </c>
+      <c r="I845" t="n">
+        <v>0</v>
+      </c>
+      <c r="J845" t="n">
+        <v>0</v>
+      </c>
+      <c r="K845" t="n">
+        <v>0</v>
+      </c>
+      <c r="L845" t="n">
+        <v>0</v>
+      </c>
+      <c r="M845" t="n">
+        <v>0</v>
+      </c>
+      <c r="N845" t="n">
+        <v>0</v>
+      </c>
+      <c r="O845" t="n">
+        <v>0</v>
+      </c>
+      <c r="P845" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q845" t="n">
+        <v>0</v>
+      </c>
+      <c r="R845" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y845"/>
+  <dimension ref="A1:Y846"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44354</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45114</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>43423</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43402</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>44210</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>43472</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>43664</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>44125</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44026</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>44498</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45177</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>44470</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44854</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44861</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44960</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>43738</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>43738</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>44418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44960</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>45182</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44015</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44139</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44860</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44986</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44987</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>45016</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45191</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45201</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>43427</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>43439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43636</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>43803</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>43888</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>43936</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44082</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44082</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44393</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44393</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44501</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44764</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44817</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44823</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44925</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44985</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45112</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45113</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45113</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45208</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>43339</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>43374</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>43440</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>43445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>43473</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>43493</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>43500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>43500</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>43501</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>43504</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>43504</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>43504</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>43504</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>43507</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>43510</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>43516</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>43517</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>43517</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>43523</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>43531</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>43536</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>43539</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43544</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>43559</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>43585</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>43585</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43585</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>43585</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>43587</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43591</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43601</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>43614</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>43636</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43664</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>43664</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>43664</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43686</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43697</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43700</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43705</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>43707</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>43709</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43738</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43738</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43738</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43739</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>43740</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43748</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>43752</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>43753</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43754</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>43755</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>43760</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>43761</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>43768</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>43768</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>43769</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>43769</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43787</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43787</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43794</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43794</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43795</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43803</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43803</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43803</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>43805</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>43810</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43818</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43833</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43841</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>43843</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>43843</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>43845</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>43852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>43859</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>43888</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>43924</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>43936</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>43936</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>43961</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>43976</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>43980</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43980</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43983</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43987</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43993</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43993</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43993</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44004</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44007</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44014</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44026</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44028</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44029</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44029</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44029</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>44029</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44029</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44050</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>44054</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>44060</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44071</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44078</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44082</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44082</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>44089</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44089</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44089</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44089</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44090</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44090</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44090</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44090</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44096</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44106</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44106</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44106</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44115</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44116</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44117</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44125</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44132</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44132</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44132</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44133</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44134</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44141</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44147</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44147</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44148</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44151</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44151</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44151</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>44152</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>44161</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44163</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44166</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44168</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44170</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44170</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44175</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44186</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44193</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44207</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44210</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44211</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44218</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44218</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44230</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44231</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44231</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44231</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44323</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44328</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44341</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44344</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44344</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44344</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44350</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44350</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>44351</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44356</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44357</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44357</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>44368</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44371</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>44377</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44377</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44377</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>44377</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44377</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44377</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44377</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>44378</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44379</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44379</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44381</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>44382</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44386</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44386</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44386</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>44386</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44391</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44390</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>44391</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44390</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44392</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44393</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44393</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>44399</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>44404</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44407</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44417</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>44418</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44420</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44420</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>44420</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44424</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44426</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44426</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44426</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44428</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44433</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44433</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44438</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44438</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44449</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44449</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44453</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>44455</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44459</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44470</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44470</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>44472</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44473</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44473</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44474</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44476</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44476</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44477</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44477</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44483</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44489</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>44490</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44490</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44496</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44496</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>44496</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44496</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44496</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44497</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44497</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44498</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44498</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44498</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44498</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44498</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>44501</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>44503</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>44503</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>44503</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44505</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44505</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44505</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>44510</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44512</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44516</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44516</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44518</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44519</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44519</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>44519</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44523</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44524</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44525</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44526</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44526</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44526</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44530</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>44531</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44533</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44533</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44551</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>44551</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44585</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44585</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44585</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44586</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44592</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44592</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44594</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44595</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44607</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44615</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44632</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44637</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44642</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44652</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44652</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44662</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44662</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44672</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44674</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44674</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44678</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44681</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44687</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44687</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>44687</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44687</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44687</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44694</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44694</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44694</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44697</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>44698</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44698</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44701</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44708</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44708</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44708</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>44708</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44708</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44708</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>44709</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44711</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44711</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44713</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>44719</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>44722</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>44726</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44726</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44727</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44728</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44728</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>44729</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44740</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>44739</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44741</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44742</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44742</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44744</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44747</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>44747</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>44749</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>44751</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44750</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44750</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44754</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44755</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44755</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44755</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>44755</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44756</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44756</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44757</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44762</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>44761</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>44761</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>44768</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>44770</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44770</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>44774</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>44775</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>44779</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44778</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44779</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44781</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44781</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44783</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44796</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44795</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>44795</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44798</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44799</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44799</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44803</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44803</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44803</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44803</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44803</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44803</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>44806</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44807</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44809</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44809</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44813</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44813</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44813</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44813</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44814</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44816</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44816</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44816</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44816</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44818</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>44818</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44818</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>44818</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44818</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44819</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44820</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44826</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>44826</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44830</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44832</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44834</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44839</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44839</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44846</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44846</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44846</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44847</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44848</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>44847</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>44852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44855</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44858</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44858</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44859</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>44859</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>44860</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44860</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44862</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>44862</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44866</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>44868</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44872</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44872</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44876</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>44879</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>44886</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>44886</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44886</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>44887</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44888</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44888</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44894</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44908</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44908</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>44908</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44908</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>44908</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44908</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>44911</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44911</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>44915</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44917</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44917</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44922</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44925</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>44925</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>44928</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>44929</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44936</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44936</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44936</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44936</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>44936</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>44936</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44936</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44937</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44938</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44938</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>44943</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>44943</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>44943</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44943</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>44950</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44950</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44951</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44952</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>44952</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44952</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44952</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44952</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44952</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44954</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44953</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44958</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44959</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44960</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44960</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44960</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44964</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44966</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44966</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44967</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44967</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44970</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44970</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44970</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44971</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44973</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44973</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44977</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44978</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>44978</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>44977</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>44980</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44984</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44984</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44984</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44985</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44985</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44986</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44986</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44986</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44987</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44988</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>44988</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>44988</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44988</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44988</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44992</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>44993</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>44993</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>44994</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45000</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45005</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45005</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45005</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45009</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45010</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45010</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45010</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45010</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45010</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45010</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45009</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45014</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45014</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>45016</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45030</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>45035</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45036</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45037</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45038</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45040</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45041</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45042</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45042</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45044</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45044</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45048</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45051</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45061</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45068</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45068</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45068</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45068</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45068</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45068</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45072</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45072</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45072</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45077</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45077</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45077</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45077</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>45078</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45078</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45078</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45078</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45078</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45078</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>45078</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45078</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45079</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45078</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45078</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45078</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45079</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45079</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45079</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45084</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45091</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45092</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45092</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45092</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>45092</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45092</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45092</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>45092</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45092</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45093</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45093</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>45093</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45096</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45098</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45098</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45099</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45099</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45099</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45099</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45099</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45099</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45103</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45103</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45103</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45103</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45103</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45103</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45103</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45103</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45103</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45103</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45105</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45107</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45107</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45112</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>45112</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45113</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45114</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45114</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>45114</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45114</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45114</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45113</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45114</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45114</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45114</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45113</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45113</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45113</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45113</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45113</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45114</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45114</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45114</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45114</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45117</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45119</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>45119</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45119</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45119</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45120</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45120</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45120</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>45120</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45121</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45121</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45121</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45126</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45127</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45135</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45135</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45140</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45147</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45147</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45147</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45149</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45149</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45149</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45149</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45152</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45154</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>45154</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45154</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45154</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45156</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45156</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45157</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45156</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46961,7 +46961,7 @@
         <v>45159</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45159</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45160</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45160</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47199,7 +47199,7 @@
         <v>45161</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45162</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45163</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45163</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45166</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45166</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45166</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45167</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45167</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45169</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45173</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45173</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45173</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45173</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45175</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45175</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45175</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45175</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45174</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45175</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45175</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45176</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>45177</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45180</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45180</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45182</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45184</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45187</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45187</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45187</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45188</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45188</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45188</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45189</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49227,7 +49227,7 @@
         <v>45189</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45189</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45190</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45190</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45191</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45194</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45196</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45196</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45198</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45198</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>45199</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45198</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45198</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45201</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45201</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45203</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45204</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45204</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45205</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45206</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45206</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45208</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45210</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45214</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>45215</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45217</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45218</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45218</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45221</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45222</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45223</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>45224</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45224</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45224</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45229</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>45233</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45235</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>45236</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>45236</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>45236</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51751,7 +51751,7 @@
         <v>45240</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>45239</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51875,7 +51875,7 @@
         <v>45240</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51937,7 +51937,7 @@
         <v>45244</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51999,7 +51999,7 @@
         <v>45244</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52061,7 +52061,7 @@
         <v>45244</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>45245</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52173,14 +52173,14 @@
     <row r="830" ht="15" customHeight="1">
       <c r="A830" t="inlineStr">
         <is>
-          <t>A 57641-2023</t>
+          <t>A 57632-2023</t>
         </is>
       </c>
       <c r="B830" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
         </is>
       </c>
       <c r="G830" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -52237,7 +52237,7 @@
         <v>45246</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52292,14 +52292,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 57632-2023</t>
+          <t>A 57800-2023</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52311,8 +52311,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G832" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -52349,14 +52354,14 @@
     <row r="833" ht="15" customHeight="1">
       <c r="A833" t="inlineStr">
         <is>
-          <t>A 57800-2023</t>
+          <t>A 57641-2023</t>
         </is>
       </c>
       <c r="B833" s="1" t="n">
-        <v>45247</v>
+        <v>45246</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52368,13 +52373,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F833" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G833" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -52418,7 +52418,7 @@
         <v>45250</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>45257</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>45257</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52599,7 +52599,7 @@
         <v>45260</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52656,7 +52656,7 @@
         <v>45261</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52713,7 +52713,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52830,14 +52830,14 @@
     <row r="841" ht="15" customHeight="1">
       <c r="A841" t="inlineStr">
         <is>
-          <t>A 61876-2023</t>
+          <t>A 61874-2023</t>
         </is>
       </c>
       <c r="B841" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52855,7 +52855,7 @@
         </is>
       </c>
       <c r="G841" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="H841" t="n">
         <v>0</v>
@@ -52892,14 +52892,14 @@
     <row r="842" ht="15" customHeight="1">
       <c r="A842" t="inlineStr">
         <is>
-          <t>A 61874-2023</t>
+          <t>A 62109-2023</t>
         </is>
       </c>
       <c r="B842" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52913,11 +52913,11 @@
       </c>
       <c r="F842" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="G842" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="H842" t="n">
         <v>0</v>
@@ -52954,14 +52954,14 @@
     <row r="843" ht="15" customHeight="1">
       <c r="A843" t="inlineStr">
         <is>
-          <t>A 61985-2023</t>
+          <t>A 61876-2023</t>
         </is>
       </c>
       <c r="B843" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52979,7 +52979,7 @@
         </is>
       </c>
       <c r="G843" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -53016,14 +53016,14 @@
     <row r="844" ht="15" customHeight="1">
       <c r="A844" t="inlineStr">
         <is>
-          <t>A 62108-2023</t>
+          <t>A 61985-2023</t>
         </is>
       </c>
       <c r="B844" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53037,11 +53037,11 @@
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="G844" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="H844" t="n">
         <v>0</v>
@@ -53075,67 +53075,129 @@
       </c>
       <c r="R844" s="2" t="inlineStr"/>
     </row>
-    <row r="845">
+    <row r="845" ht="15" customHeight="1">
       <c r="A845" t="inlineStr">
         <is>
-          <t>A 62109-2023</t>
+          <t>A 62108-2023</t>
         </is>
       </c>
       <c r="B845" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="C845" s="1" t="n">
+        <v>45268</v>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>ÅSELE</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="G845" t="n">
+        <v>4</v>
+      </c>
+      <c r="H845" t="n">
+        <v>0</v>
+      </c>
+      <c r="I845" t="n">
+        <v>0</v>
+      </c>
+      <c r="J845" t="n">
+        <v>0</v>
+      </c>
+      <c r="K845" t="n">
+        <v>0</v>
+      </c>
+      <c r="L845" t="n">
+        <v>0</v>
+      </c>
+      <c r="M845" t="n">
+        <v>0</v>
+      </c>
+      <c r="N845" t="n">
+        <v>0</v>
+      </c>
+      <c r="O845" t="n">
+        <v>0</v>
+      </c>
+      <c r="P845" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q845" t="n">
+        <v>0</v>
+      </c>
+      <c r="R845" s="2" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>A 62353-2023</t>
+        </is>
+      </c>
+      <c r="B846" s="1" t="n">
         <v>45267</v>
       </c>
-      <c r="D845" t="inlineStr">
-        <is>
-          <t>VÄSTERBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="E845" t="inlineStr">
-        <is>
-          <t>ÅSELE</t>
-        </is>
-      </c>
-      <c r="F845" t="inlineStr">
+      <c r="C846" s="1" t="n">
+        <v>45268</v>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>ÅSELE</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
         <is>
           <t>SCA</t>
         </is>
       </c>
-      <c r="G845" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H845" t="n">
-        <v>0</v>
-      </c>
-      <c r="I845" t="n">
-        <v>0</v>
-      </c>
-      <c r="J845" t="n">
-        <v>0</v>
-      </c>
-      <c r="K845" t="n">
-        <v>0</v>
-      </c>
-      <c r="L845" t="n">
-        <v>0</v>
-      </c>
-      <c r="M845" t="n">
-        <v>0</v>
-      </c>
-      <c r="N845" t="n">
-        <v>0</v>
-      </c>
-      <c r="O845" t="n">
-        <v>0</v>
-      </c>
-      <c r="P845" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q845" t="n">
-        <v>0</v>
-      </c>
-      <c r="R845" s="2" t="inlineStr"/>
+      <c r="G846" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H846" t="n">
+        <v>0</v>
+      </c>
+      <c r="I846" t="n">
+        <v>0</v>
+      </c>
+      <c r="J846" t="n">
+        <v>0</v>
+      </c>
+      <c r="K846" t="n">
+        <v>0</v>
+      </c>
+      <c r="L846" t="n">
+        <v>0</v>
+      </c>
+      <c r="M846" t="n">
+        <v>0</v>
+      </c>
+      <c r="N846" t="n">
+        <v>0</v>
+      </c>
+      <c r="O846" t="n">
+        <v>0</v>
+      </c>
+      <c r="P846" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q846" t="n">
+        <v>0</v>
+      </c>
+      <c r="R846" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -564,7 +564,7 @@
         <v>44354</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45114</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>43423</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43402</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>44210</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>43472</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>43664</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>44125</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44026</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>44498</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45177</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>44470</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44854</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44861</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44960</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>43738</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>43738</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>44418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44960</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>45182</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44015</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44139</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44860</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44986</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44987</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>45016</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45191</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45201</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>43427</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>43439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43636</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>43803</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>43888</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>43936</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44082</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44082</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44393</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44393</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44501</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44764</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44817</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44823</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44925</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44985</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45112</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45113</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45113</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45208</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>43339</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>43374</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>43440</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>43445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>43473</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>43493</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>43500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>43500</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>43501</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>43504</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>43504</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>43504</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>43504</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>43507</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>43510</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>43516</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>43517</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>43517</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>43523</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>43531</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>43536</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>43539</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43544</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>43559</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>43585</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>43585</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43585</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>43585</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>43587</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43591</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43601</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>43614</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>43636</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43664</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>43664</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>43664</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43686</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43697</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43700</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43705</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>43707</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>43709</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43738</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43738</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43738</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43739</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>43740</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43748</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>43752</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>43753</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43754</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>43755</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>43760</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>43761</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>43768</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>43768</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>43769</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>43769</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43787</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43787</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43794</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43794</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43795</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43803</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43803</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43803</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>43805</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>43810</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43818</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43833</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43841</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>43843</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>43843</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>43845</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>43852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>43859</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>43888</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>43924</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>43936</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>43936</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>43961</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>43976</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>43980</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43980</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43983</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43987</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43993</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43993</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43993</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44004</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44007</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44014</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44026</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44028</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44029</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44029</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44029</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>44029</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44029</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44050</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>44054</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>44060</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44071</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44078</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44082</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44082</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>44089</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44089</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44089</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44089</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44090</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44090</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44090</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44090</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44096</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44106</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44106</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44106</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44115</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44116</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44117</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44125</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44132</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44132</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44132</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44133</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44134</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44141</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44147</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44147</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44148</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44151</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44151</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44151</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>44152</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>44161</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44163</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44166</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44168</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44170</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44170</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44175</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44186</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44193</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44207</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44210</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44211</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44218</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44218</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44230</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44231</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44231</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44231</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44323</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44328</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44341</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44344</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44344</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44344</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44350</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44350</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>44351</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44356</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44357</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44357</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>44368</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44371</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>44377</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44377</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44377</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>44377</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44377</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44377</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44377</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>44378</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44379</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44379</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44381</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>44382</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44386</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44386</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44386</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>44386</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44391</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44390</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>44391</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44390</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44392</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44393</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44393</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>44399</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>44404</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44407</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44417</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>44418</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44420</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44420</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>44420</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44424</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44426</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44426</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44426</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44428</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44433</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44433</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44438</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44438</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44449</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44449</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44453</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>44455</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44459</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44470</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44470</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>44472</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44473</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44473</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44474</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44476</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44476</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44477</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44477</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44483</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44489</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>44490</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44490</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44496</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44496</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>44496</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44496</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44496</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44497</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44497</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44498</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44498</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44498</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44498</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44498</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>44501</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>44503</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>44503</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>44503</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44505</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44505</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44505</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>44510</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44512</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44516</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44516</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44518</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44519</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44519</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>44519</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44523</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44524</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44525</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44526</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44526</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44526</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44530</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>44531</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44533</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44533</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44551</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>44551</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44585</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44585</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44585</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44586</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44592</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44592</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44594</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44595</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44607</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44615</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44632</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44637</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44642</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44652</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44652</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44662</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44662</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44672</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44674</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44674</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44678</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44681</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44687</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44687</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>44687</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44687</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44687</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44694</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44694</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44694</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44697</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>44698</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44698</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44701</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44708</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44708</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44708</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>44708</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44708</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44708</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>44709</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44711</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44711</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44713</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>44719</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>44722</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>44726</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44726</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44727</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44728</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44728</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>44729</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44740</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>44739</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44741</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44742</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44742</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44744</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44747</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>44747</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>44749</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>44751</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44750</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44750</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44754</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44755</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44755</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44755</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>44755</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44756</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44756</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44757</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44762</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>44761</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>44761</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>44768</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>44770</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44770</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>44774</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>44775</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>44779</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44778</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44779</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44781</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44781</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44783</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44796</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44795</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>44795</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44798</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44799</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44799</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44803</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44803</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44803</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44803</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44803</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44803</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>44806</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44807</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44809</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44809</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44813</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44813</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44813</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44813</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44814</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44816</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44816</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44816</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44816</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44818</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>44818</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44818</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>44818</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44818</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44819</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44820</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44826</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>44826</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44830</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44832</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44834</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44839</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44839</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44846</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44846</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44846</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44847</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44848</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>44847</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>44852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44855</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44858</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44858</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44859</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>44859</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>44860</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44860</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44862</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>44862</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44866</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>44868</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44872</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44872</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44876</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>44879</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>44886</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>44886</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44886</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>44887</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44888</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44888</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44894</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44908</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44908</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>44908</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44908</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>44908</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44908</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>44911</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44911</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>44915</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44917</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44917</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44922</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44925</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>44925</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>44928</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>44929</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44936</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44936</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44936</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44936</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>44936</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>44936</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44936</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44937</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44938</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44938</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>44943</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>44943</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>44943</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44943</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>44950</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44950</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44951</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44952</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>44952</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44952</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44952</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44952</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44952</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44954</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44953</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44958</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44959</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44960</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44960</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44960</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44964</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44966</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44966</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44967</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44967</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44970</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44970</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44970</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44971</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44973</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44973</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44977</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44978</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>44978</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>44977</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>44980</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44984</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44984</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44984</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44985</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44985</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44986</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44986</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44986</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44987</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44988</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>44988</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>44988</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44988</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44988</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44992</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>44993</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>44993</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>44994</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45000</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45005</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45005</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45005</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45009</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45010</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45010</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45010</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45010</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45010</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45010</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45009</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45014</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45014</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>45016</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45030</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>45035</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45036</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45037</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45038</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45040</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45041</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45042</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45042</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45044</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45044</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45048</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45051</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45061</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45068</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45068</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45068</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45068</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45068</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45068</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45072</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45072</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45072</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45077</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45077</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45077</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45077</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>45078</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45078</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45078</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45078</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45078</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45078</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>45078</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45078</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45079</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45078</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45078</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45078</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45079</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45079</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45079</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45084</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45091</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45092</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45092</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45092</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>45092</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45092</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45092</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>45092</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45092</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45093</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45093</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>45093</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45096</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45098</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45098</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45099</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45099</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45099</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45099</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45099</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45099</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45103</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45103</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45103</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45103</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45103</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45103</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45103</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45103</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45103</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45103</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45105</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45107</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45107</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45112</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>45112</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45113</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45114</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45114</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>45114</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45114</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45114</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45113</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45114</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45114</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45114</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45113</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45113</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45113</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45113</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45113</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45114</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45114</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45114</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45114</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45117</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45119</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>45119</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45119</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45119</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45120</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45120</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45120</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>45120</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45121</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45121</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45121</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45126</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45127</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45135</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45135</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45140</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45147</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45147</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45147</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45149</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45149</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45149</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45149</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45152</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45154</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>45154</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45154</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45154</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45156</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45156</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45157</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45156</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46961,7 +46961,7 @@
         <v>45159</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45159</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45160</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45160</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47199,7 +47199,7 @@
         <v>45161</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45162</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45163</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45163</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45166</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45166</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45166</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45167</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45167</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45169</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45173</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45173</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45173</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45173</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45175</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45175</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45175</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45175</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45174</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45175</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45175</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45176</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>45177</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45180</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45180</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45182</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45184</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45187</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45187</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45187</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45188</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45188</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45188</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45189</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49227,7 +49227,7 @@
         <v>45189</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45189</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45190</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45190</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45191</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45194</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45196</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45196</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45198</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45198</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>45199</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45198</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45198</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45201</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45201</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45203</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45204</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45204</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45205</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45206</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45206</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45208</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45210</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45214</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>45215</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45217</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45218</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45218</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45221</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45222</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45223</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>45224</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45224</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45224</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45229</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>45233</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45235</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>45236</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>45236</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>45236</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51751,7 +51751,7 @@
         <v>45240</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>45239</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51875,7 +51875,7 @@
         <v>45240</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51930,14 +51930,14 @@
     <row r="826" ht="15" customHeight="1">
       <c r="A826" t="inlineStr">
         <is>
-          <t>A 56826-2023</t>
+          <t>A 56961-2023</t>
         </is>
       </c>
       <c r="B826" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51951,11 +51951,11 @@
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>Naturvårdsverket</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="G826" t="n">
-        <v>2.5</v>
+        <v>10.8</v>
       </c>
       <c r="H826" t="n">
         <v>0</v>
@@ -51992,14 +51992,14 @@
     <row r="827" ht="15" customHeight="1">
       <c r="A827" t="inlineStr">
         <is>
-          <t>A 56961-2023</t>
+          <t>A 56826-2023</t>
         </is>
       </c>
       <c r="B827" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52013,11 +52013,11 @@
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Naturvårdsverket</t>
         </is>
       </c>
       <c r="G827" t="n">
-        <v>10.8</v>
+        <v>2.5</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -52061,7 +52061,7 @@
         <v>45244</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>45245</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>45246</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52230,14 +52230,14 @@
     <row r="831" ht="15" customHeight="1">
       <c r="A831" t="inlineStr">
         <is>
-          <t>A 57788-2023</t>
+          <t>A 57641-2023</t>
         </is>
       </c>
       <c r="B831" s="1" t="n">
         <v>45246</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52249,13 +52249,8 @@
           <t>ÅSELE</t>
         </is>
       </c>
-      <c r="F831" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="G831" t="n">
-        <v>7.7</v>
+        <v>2.6</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -52292,14 +52287,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 57800-2023</t>
+          <t>A 57788-2023</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
-        <v>45247</v>
+        <v>45246</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52317,7 +52312,7 @@
         </is>
       </c>
       <c r="G832" t="n">
-        <v>1.5</v>
+        <v>7.7</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -52354,14 +52349,14 @@
     <row r="833" ht="15" customHeight="1">
       <c r="A833" t="inlineStr">
         <is>
-          <t>A 57641-2023</t>
+          <t>A 57800-2023</t>
         </is>
       </c>
       <c r="B833" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52373,8 +52368,13 @@
           <t>ÅSELE</t>
         </is>
       </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="G833" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -52418,7 +52418,7 @@
         <v>45250</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>45257</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>45257</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52599,7 +52599,7 @@
         <v>45260</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52656,7 +52656,7 @@
         <v>45261</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52706,14 +52706,14 @@
     <row r="839" ht="15" customHeight="1">
       <c r="A839" t="inlineStr">
         <is>
-          <t>A 61800-2023</t>
+          <t>A 61801-2023</t>
         </is>
       </c>
       <c r="B839" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         </is>
       </c>
       <c r="G839" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -52768,14 +52768,14 @@
     <row r="840" ht="15" customHeight="1">
       <c r="A840" t="inlineStr">
         <is>
-          <t>A 61801-2023</t>
+          <t>A 61800-2023</t>
         </is>
       </c>
       <c r="B840" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         </is>
       </c>
       <c r="G840" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="H840" t="n">
         <v>0</v>
@@ -52830,14 +52830,14 @@
     <row r="841" ht="15" customHeight="1">
       <c r="A841" t="inlineStr">
         <is>
-          <t>A 61874-2023</t>
+          <t>A 62108-2023</t>
         </is>
       </c>
       <c r="B841" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52851,11 +52851,11 @@
       </c>
       <c r="F841" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="G841" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="H841" t="n">
         <v>0</v>
@@ -52892,14 +52892,14 @@
     <row r="842" ht="15" customHeight="1">
       <c r="A842" t="inlineStr">
         <is>
-          <t>A 62109-2023</t>
+          <t>A 61876-2023</t>
         </is>
       </c>
       <c r="B842" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52913,11 +52913,11 @@
       </c>
       <c r="F842" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="G842" t="n">
-        <v>1.1</v>
+        <v>6.3</v>
       </c>
       <c r="H842" t="n">
         <v>0</v>
@@ -52954,14 +52954,14 @@
     <row r="843" ht="15" customHeight="1">
       <c r="A843" t="inlineStr">
         <is>
-          <t>A 61876-2023</t>
+          <t>A 61985-2023</t>
         </is>
       </c>
       <c r="B843" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52979,7 +52979,7 @@
         </is>
       </c>
       <c r="G843" t="n">
-        <v>6.3</v>
+        <v>2.4</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -53016,14 +53016,14 @@
     <row r="844" ht="15" customHeight="1">
       <c r="A844" t="inlineStr">
         <is>
-          <t>A 61985-2023</t>
+          <t>A 61874-2023</t>
         </is>
       </c>
       <c r="B844" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53041,7 +53041,7 @@
         </is>
       </c>
       <c r="G844" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="H844" t="n">
         <v>0</v>
@@ -53078,14 +53078,14 @@
     <row r="845" ht="15" customHeight="1">
       <c r="A845" t="inlineStr">
         <is>
-          <t>A 62108-2023</t>
+          <t>A 62109-2023</t>
         </is>
       </c>
       <c r="B845" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         </is>
       </c>
       <c r="G845" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="H845" t="n">
         <v>0</v>
@@ -53147,7 +53147,7 @@
         <v>45267</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>

--- a/Översikt ÅSELE.xlsx
+++ b/Översikt ÅSELE.xlsx
@@ -564,7 +564,7 @@
         <v>44354</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45114</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>44960</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>43423</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>43402</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>44210</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>43472</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>43664</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>44125</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>44026</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>44498</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45177</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>44470</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>44854</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>44861</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>44960</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>43738</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>43738</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>44418</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44960</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>45182</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44015</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44139</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44860</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>44951</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>44986</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44987</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>45016</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>45191</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45201</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>43427</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>43439</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>43636</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>43803</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>43888</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>43936</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44082</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44082</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44393</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44393</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44501</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>44764</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>44817</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44823</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44925</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44985</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45112</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45113</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45113</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>45208</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>43318</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>43339</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>43374</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>43423</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>43424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>43427</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>43440</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>43445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>43473</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>43479</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>43493</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>43500</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>43500</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>43501</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>43504</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>43504</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>43504</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>43504</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>43507</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>43510</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>43516</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>43517</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>43517</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>43523</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>43531</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>43536</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>43539</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>43544</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>43559</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>43585</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>43585</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43585</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>43585</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>43587</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>43591</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>43601</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>43614</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>43636</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>43664</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>43664</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>43664</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43686</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43697</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43700</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43705</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>43707</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>43709</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43738</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>43738</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>43738</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43739</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>43740</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43748</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>43752</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>43753</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>43754</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>43755</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>43760</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>43761</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>43768</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>43768</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>43769</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>43769</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>43787</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>43787</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>43794</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>43794</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>43795</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>43803</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>43803</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>43803</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>43805</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>43810</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43818</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>43833</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43841</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>43843</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>43843</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>43845</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>43852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>43859</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>43888</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>43924</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>43936</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>43936</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>43961</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>43976</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>43980</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>43980</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>43983</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43987</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43993</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43993</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>43993</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44004</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44007</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44014</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44026</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44028</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44029</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44029</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44029</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>44029</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44029</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44050</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>44054</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>44060</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44071</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>44078</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44082</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44082</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>44089</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44089</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44089</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44089</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44090</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44090</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44090</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44090</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44096</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44106</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44106</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44106</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44115</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44116</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44117</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44125</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44132</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44132</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44132</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44133</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>44134</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44141</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44147</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44147</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44148</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44151</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44151</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44151</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>44152</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>44161</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>44163</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44166</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44168</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44170</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>44170</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44171</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44171</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44175</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44186</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44193</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44207</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>44210</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44211</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44218</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44218</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44230</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44231</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44231</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44231</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44323</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44328</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44341</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44344</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44344</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>44344</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44350</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44350</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>44351</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44356</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44357</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>44357</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>44368</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44371</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>44377</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>44377</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44377</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>44377</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44377</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44377</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44377</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>44378</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44379</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44379</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44381</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>44382</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44386</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>44386</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44386</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>44386</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44391</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44390</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>44391</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44390</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44392</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>44393</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44393</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>44399</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>44404</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>44407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44407</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44417</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>44418</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44420</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>44420</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>44420</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44424</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44426</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>44426</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>44426</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44428</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44433</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44433</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44438</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>44438</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44449</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44449</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44453</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>44455</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44459</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44470</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44470</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>44472</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44473</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44473</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>44474</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>44476</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44476</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44477</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44477</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44483</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44489</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>44490</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44490</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44496</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44496</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>44496</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44496</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44496</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44497</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44497</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44498</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44498</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>44498</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44498</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>44498</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>44501</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>44503</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>44503</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>44503</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44505</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44505</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44505</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>44510</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44512</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44516</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44516</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44518</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44519</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44519</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>44519</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44523</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44524</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44525</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>44526</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44526</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44526</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44530</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>44531</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44533</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44533</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44551</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>44551</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44585</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44585</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44585</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44586</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44592</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44592</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>44593</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44594</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44595</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44607</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22530,7 +22530,7 @@
         <v>44615</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44632</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>44637</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44642</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44652</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44652</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44662</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44662</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>44672</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>44674</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44674</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44678</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44681</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44687</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44687</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>44687</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>44687</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>44687</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>44694</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44694</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>44694</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44697</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>44698</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44698</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44701</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44708</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44708</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44708</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>44708</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44708</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44708</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>44709</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44711</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44711</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44713</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>44719</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>44722</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>44726</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44726</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44727</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44728</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44728</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>44729</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44740</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>44739</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>44741</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44742</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44742</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44744</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44747</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>44747</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>44749</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>44751</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44750</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44750</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44754</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44755</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44755</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44755</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>44755</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44756</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>44756</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>44757</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>44762</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>44761</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>44761</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>44768</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>44770</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44770</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>44774</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>44775</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>44779</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44778</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44779</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44781</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44781</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44783</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44796</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44795</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>44795</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44798</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>44799</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>44799</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>44803</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>44803</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>44803</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44803</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44803</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44803</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>44806</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44807</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44809</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44809</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44813</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44813</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44813</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44813</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44814</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44816</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44816</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>44816</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>44816</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44818</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>44818</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44818</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>44818</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>44818</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44819</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44820</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44826</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>44826</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44830</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>44832</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44834</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44839</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44839</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44846</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44846</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44846</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44847</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44848</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>44847</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>44852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44855</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44858</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44858</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>44859</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>44859</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>44860</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>44860</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44862</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>44862</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44866</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>44868</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44872</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44872</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>44876</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>44879</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>44886</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>44886</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44886</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>44887</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>44888</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44888</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>44894</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>44908</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>44908</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>44908</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44908</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>44908</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44908</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>44911</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44911</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>44915</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44917</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44917</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>44922</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44925</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>44925</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>44928</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>44929</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44936</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>44936</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44936</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44936</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>44936</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>44936</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>44936</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>44937</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44938</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>44938</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>44943</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>44943</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>44943</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>44943</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>44950</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>44950</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44951</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44952</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>44952</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44952</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44952</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44952</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44952</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>44954</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44953</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44958</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44959</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>44960</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44960</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44960</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44964</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>44966</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44966</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>44967</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44967</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>44970</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44970</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>44970</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>44971</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44971</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>44971</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>44973</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44973</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>44977</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44978</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>44978</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>44977</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>44980</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44984</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44984</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44984</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44985</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44985</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>44986</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>44986</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44986</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>44987</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>44988</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>44988</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>44988</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44988</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44988</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44992</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>44993</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>44993</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>44994</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45000</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45005</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45005</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45005</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45009</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45010</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45010</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45010</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45010</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45010</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45010</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>45009</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45014</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45014</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>45016</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>45030</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37643,7 +37643,7 @@
         <v>45035</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>45036</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>45037</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45038</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45040</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45041</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45042</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45042</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         <v>45044</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45044</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45048</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45051</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45061</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45068</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45068</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45068</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45068</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45068</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45068</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45072</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45072</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45072</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45077</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45077</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45077</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45077</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>45078</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45078</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45078</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45078</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39604,7 +39604,7 @@
         <v>45078</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45078</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>45078</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45078</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45079</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45078</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>45078</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45078</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45079</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45079</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45079</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45084</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45091</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45092</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45092</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45092</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>45092</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45092</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>45092</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>45092</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45092</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45093</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45093</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>45093</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45096</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>45098</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45098</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45099</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45099</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45099</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>45099</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45099</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45099</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45103</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45103</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>45103</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>45103</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45103</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45103</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45103</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45103</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45103</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45103</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45104</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45104</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45105</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42602,7 +42602,7 @@
         <v>45105</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45105</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45105</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45105</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45105</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45105</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45107</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>45107</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>45107</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>45107</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45107</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45112</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45112</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>45112</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45112</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43579,7 +43579,7 @@
         <v>45113</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45114</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45114</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>45114</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45114</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45114</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45113</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45114</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45114</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>45114</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45113</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45113</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45113</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45113</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45113</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45113</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45114</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45114</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>45114</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45114</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45117</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45119</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>45119</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>45119</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>45119</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45120</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45120</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45120</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>45120</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45121</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45121</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45121</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45126</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45127</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45135</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45135</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45140</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45147</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>45147</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45147</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45149</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46227,7 +46227,7 @@
         <v>45149</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>45149</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45149</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45152</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45154</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>45154</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45154</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45154</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45156</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45156</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45157</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45156</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46961,7 +46961,7 @@
         <v>45159</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>45159</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45160</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45160</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47199,7 +47199,7 @@
         <v>45161</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45162</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45163</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45163</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45166</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45166</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45166</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45167</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45167</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45169</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45173</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45173</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45173</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45173</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45175</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45175</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45175</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>45175</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45174</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45175</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45175</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45176</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>45177</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45180</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45180</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45182</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45184</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45187</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45187</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45187</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45188</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45188</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45188</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45189</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49227,7 +49227,7 @@
         <v>45189</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45189</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45190</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45190</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45191</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45194</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45196</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45196</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45198</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45198</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>45199</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>45198</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45198</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45201</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45201</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45203</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45204</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45204</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45205</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45206</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45206</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45208</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45210</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45215</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45214</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>45215</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45217</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45217</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45218</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45218</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45221</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45222</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45223</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>45224</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45224</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45224</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45229</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>45233</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45235</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>45236</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>45236</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>45236</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51751,7 +51751,7 @@
         <v>45240</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>45239</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51875,7 +51875,7 @@
         <v>45240</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -519